--- a/research/traditional_assets/database/data/portugal/portugal_oil_gas_integrated.xlsx
+++ b/research/traditional_assets/database/data/portugal/portugal_oil_gas_integrated.xlsx
@@ -1284,7 +1284,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1421,22 +1421,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1012473666785821</v>
+        <v>0.1010702972085571</v>
       </c>
       <c r="C2">
-        <v>17544.20933383481</v>
+        <v>17392.78339019973</v>
       </c>
       <c r="D2">
-        <v>15296.80933383481</v>
+        <v>15322.77539019973</v>
       </c>
       <c r="E2">
-        <v>-5330.1</v>
+        <v>-5152.708000000001</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>177.392</v>
       </c>
       <c r="G2">
         <v>2247.4</v>
@@ -1457,28 +1457,28 @@
         <v>2683.5</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>8.9228176</v>
       </c>
       <c r="N2">
-        <v>2683.5</v>
+        <v>2674.5771824</v>
       </c>
       <c r="O2">
-        <v>563.535</v>
+        <v>561.661208304</v>
       </c>
       <c r="P2">
-        <v>2119.965</v>
+        <v>2112.915974096</v>
       </c>
       <c r="Q2">
-        <v>3011.065</v>
+        <v>3004.015974096</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1012473666785821</v>
+        <v>0.101689825463189</v>
       </c>
       <c r="T2">
-        <v>0.934922259086021</v>
+        <v>0.9423827498403438</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1495,7 +1495,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>300.7458092609671</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1503,22 +1503,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1010702972085571</v>
+        <v>0.1008932277385321</v>
       </c>
       <c r="C3">
-        <v>17392.78339019973</v>
+        <v>17241.44575027792</v>
       </c>
       <c r="D3">
-        <v>15322.77539019973</v>
+        <v>15348.82975027792</v>
       </c>
       <c r="E3">
-        <v>-5152.708000000001</v>
+        <v>-4975.316000000001</v>
       </c>
       <c r="F3">
-        <v>177.392</v>
+        <v>354.784</v>
       </c>
       <c r="G3">
         <v>2247.4</v>
@@ -1539,28 +1539,28 @@
         <v>2683.5</v>
       </c>
       <c r="M3">
-        <v>8.9228176</v>
+        <v>17.8456352</v>
       </c>
       <c r="N3">
-        <v>2674.5771824</v>
+        <v>2665.6543648</v>
       </c>
       <c r="O3">
-        <v>561.661208304</v>
+        <v>559.7874166080001</v>
       </c>
       <c r="P3">
-        <v>2112.915974096</v>
+        <v>2105.866948192</v>
       </c>
       <c r="Q3">
-        <v>3004.015974096</v>
+        <v>2996.966948192</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.101689825463189</v>
+        <v>0.1021413140189103</v>
       </c>
       <c r="T3">
-        <v>0.9423827498403438</v>
+        <v>0.9499954955080202</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>300.7458092609671</v>
+        <v>150.3729046304835</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1585,22 +1585,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1008932277385321</v>
+        <v>0.100716158268507</v>
       </c>
       <c r="C4">
-        <v>17241.44575027792</v>
+        <v>17090.19686528309</v>
       </c>
       <c r="D4">
-        <v>15348.82975027792</v>
+        <v>15374.97286528309</v>
       </c>
       <c r="E4">
-        <v>-4975.316000000001</v>
+        <v>-4797.924</v>
       </c>
       <c r="F4">
-        <v>354.784</v>
+        <v>532.176</v>
       </c>
       <c r="G4">
         <v>2247.4</v>
@@ -1621,28 +1621,28 @@
         <v>2683.5</v>
       </c>
       <c r="M4">
-        <v>17.8456352</v>
+        <v>26.7684528</v>
       </c>
       <c r="N4">
-        <v>2665.6543648</v>
+        <v>2656.7315472</v>
       </c>
       <c r="O4">
-        <v>559.7874166080001</v>
+        <v>557.9136249119999</v>
       </c>
       <c r="P4">
-        <v>2105.866948192</v>
+        <v>2098.817922288</v>
       </c>
       <c r="Q4">
-        <v>2996.966948192</v>
+        <v>2989.917922288</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1021413140189103</v>
+        <v>0.1026021116170176</v>
       </c>
       <c r="T4">
-        <v>0.9499954955080202</v>
+        <v>0.9577652050038959</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>150.3729046304835</v>
+        <v>100.248603086989</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1667,22 +1667,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.100716158268507</v>
+        <v>0.100539088798482</v>
       </c>
       <c r="C5">
-        <v>17090.19686528309</v>
+        <v>16939.03718950836</v>
       </c>
       <c r="D5">
-        <v>15374.97286528309</v>
+        <v>15401.20518950836</v>
       </c>
       <c r="E5">
-        <v>-4797.924</v>
+        <v>-4620.532</v>
       </c>
       <c r="F5">
-        <v>532.176</v>
+        <v>709.5680000000001</v>
       </c>
       <c r="G5">
         <v>2247.4</v>
@@ -1703,28 +1703,28 @@
         <v>2683.5</v>
       </c>
       <c r="M5">
-        <v>26.7684528</v>
+        <v>35.6912704</v>
       </c>
       <c r="N5">
-        <v>2656.7315472</v>
+        <v>2647.8087296</v>
       </c>
       <c r="O5">
-        <v>557.9136249119999</v>
+        <v>556.0398332159999</v>
       </c>
       <c r="P5">
-        <v>2098.817922288</v>
+        <v>2091.768896384</v>
       </c>
       <c r="Q5">
-        <v>2989.917922288</v>
+        <v>2982.868896384</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1026021116170176</v>
+        <v>0.1030725091650854</v>
       </c>
       <c r="T5">
-        <v>0.9577652050038959</v>
+        <v>0.9656967834476026</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>100.248603086989</v>
+        <v>75.18645231524177</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1749,22 +1749,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.100539088798482</v>
+        <v>0.100362019328457</v>
       </c>
       <c r="C6">
-        <v>16939.03718950836</v>
+        <v>16787.96718035251</v>
       </c>
       <c r="D6">
-        <v>15401.20518950836</v>
+        <v>15427.52718035251</v>
       </c>
       <c r="E6">
-        <v>-4620.532</v>
+        <v>-4443.14</v>
       </c>
       <c r="F6">
-        <v>709.5680000000001</v>
+        <v>886.96</v>
       </c>
       <c r="G6">
         <v>2247.4</v>
@@ -1785,28 +1785,28 @@
         <v>2683.5</v>
       </c>
       <c r="M6">
-        <v>35.6912704</v>
+        <v>44.614088</v>
       </c>
       <c r="N6">
-        <v>2647.8087296</v>
+        <v>2638.885912</v>
       </c>
       <c r="O6">
-        <v>556.0398332159999</v>
+        <v>554.16604152</v>
       </c>
       <c r="P6">
-        <v>2091.768896384</v>
+        <v>2084.71987048</v>
       </c>
       <c r="Q6">
-        <v>2982.868896384</v>
+        <v>2975.81987048</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1030725091650854</v>
+        <v>0.1035528098194284</v>
       </c>
       <c r="T6">
-        <v>0.9656967834476026</v>
+        <v>0.9737953424901241</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1823,7 +1823,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>75.18645231524177</v>
+        <v>60.14916185219342</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1831,22 +1831,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.100362019328457</v>
+        <v>0.100184949858432</v>
       </c>
       <c r="C7">
-        <v>16787.96718035251</v>
+        <v>16636.98729834664</v>
       </c>
       <c r="D7">
-        <v>15427.52718035251</v>
+        <v>15453.93929834664</v>
       </c>
       <c r="E7">
-        <v>-4443.14</v>
+        <v>-4265.748000000001</v>
       </c>
       <c r="F7">
-        <v>886.96</v>
+        <v>1064.352</v>
       </c>
       <c r="G7">
         <v>2247.4</v>
@@ -1867,28 +1867,28 @@
         <v>2683.5</v>
       </c>
       <c r="M7">
-        <v>44.614088</v>
+        <v>53.5369056</v>
       </c>
       <c r="N7">
-        <v>2638.885912</v>
+        <v>2629.9630944</v>
       </c>
       <c r="O7">
-        <v>554.16604152</v>
+        <v>552.292249824</v>
       </c>
       <c r="P7">
-        <v>2084.71987048</v>
+        <v>2077.670844576</v>
       </c>
       <c r="Q7">
-        <v>2975.81987048</v>
+        <v>2968.770844576</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1035528098194284</v>
+        <v>0.1040433296366298</v>
       </c>
       <c r="T7">
-        <v>0.9737953424901241</v>
+        <v>0.9820662112995076</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1905,7 +1905,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>60.14916185219342</v>
+        <v>50.12430154349451</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1913,22 +1913,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.100184949858432</v>
+        <v>0.100007880388407</v>
       </c>
       <c r="C8">
-        <v>16636.98729834664</v>
+        <v>16486.098007181</v>
       </c>
       <c r="D8">
-        <v>15453.93929834664</v>
+        <v>15480.442007181</v>
       </c>
       <c r="E8">
-        <v>-4265.748000000001</v>
+        <v>-4088.356000000001</v>
       </c>
       <c r="F8">
-        <v>1064.352</v>
+        <v>1241.744</v>
       </c>
       <c r="G8">
         <v>2247.4</v>
@@ -1949,28 +1949,28 @@
         <v>2683.5</v>
       </c>
       <c r="M8">
-        <v>53.5369056</v>
+        <v>62.45972319999999</v>
       </c>
       <c r="N8">
-        <v>2629.9630944</v>
+        <v>2621.0402768</v>
       </c>
       <c r="O8">
-        <v>552.292249824</v>
+        <v>550.418458128</v>
       </c>
       <c r="P8">
-        <v>2077.670844576</v>
+        <v>2070.621818672</v>
       </c>
       <c r="Q8">
-        <v>2968.770844576</v>
+        <v>2961.721818672</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1040433296366298</v>
+        <v>0.1045443982671043</v>
       </c>
       <c r="T8">
-        <v>0.9820662112995076</v>
+        <v>0.9905149482553297</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1987,7 +1987,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>50.12430154349451</v>
+        <v>42.96368703728101</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1995,22 +1995,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.100007880388407</v>
+        <v>0.09983081091838193</v>
       </c>
       <c r="C9">
-        <v>16486.098007181</v>
+        <v>16335.2997737321</v>
       </c>
       <c r="D9">
-        <v>15480.442007181</v>
+        <v>15507.0357737321</v>
       </c>
       <c r="E9">
-        <v>-4088.356</v>
+        <v>-3910.964</v>
       </c>
       <c r="F9">
-        <v>1241.744</v>
+        <v>1419.136</v>
       </c>
       <c r="G9">
         <v>2247.4</v>
@@ -2031,28 +2031,28 @@
         <v>2683.5</v>
       </c>
       <c r="M9">
-        <v>62.45972320000001</v>
+        <v>71.3825408</v>
       </c>
       <c r="N9">
-        <v>2621.0402768</v>
+        <v>2612.1174592</v>
       </c>
       <c r="O9">
-        <v>550.418458128</v>
+        <v>548.544666432</v>
       </c>
       <c r="P9">
-        <v>2070.621818672</v>
+        <v>2063.572792768</v>
       </c>
       <c r="Q9">
-        <v>2961.721818672</v>
+        <v>2954.672792768</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1045443982671043</v>
+        <v>0.1050563596938934</v>
       </c>
       <c r="T9">
-        <v>0.9905149482553297</v>
+        <v>0.9991473534058433</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>42.96368703728101</v>
+        <v>37.59322615762089</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2077,22 +2077,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.09983081091838193</v>
+        <v>0.0996537414483569</v>
       </c>
       <c r="C10">
-        <v>16335.2997737321</v>
+        <v>16184.59306809018</v>
       </c>
       <c r="D10">
-        <v>15507.0357737321</v>
+        <v>15533.72106809018</v>
       </c>
       <c r="E10">
-        <v>-3910.964</v>
+        <v>-3733.572</v>
       </c>
       <c r="F10">
-        <v>1419.136</v>
+        <v>1596.528</v>
       </c>
       <c r="G10">
         <v>2247.4</v>
@@ -2113,28 +2113,28 @@
         <v>2683.5</v>
       </c>
       <c r="M10">
-        <v>71.3825408</v>
+        <v>80.3053584</v>
       </c>
       <c r="N10">
-        <v>2612.1174592</v>
+        <v>2603.1946416</v>
       </c>
       <c r="O10">
-        <v>548.544666432</v>
+        <v>546.670874736</v>
       </c>
       <c r="P10">
-        <v>2063.572792768</v>
+        <v>2056.523766864</v>
       </c>
       <c r="Q10">
-        <v>2954.672792768</v>
+        <v>2947.623766864</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1050563596938934</v>
+        <v>0.1055795730201724</v>
       </c>
       <c r="T10">
-        <v>0.9991473534058433</v>
+        <v>1.007969481746478</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>37.59322615762089</v>
+        <v>33.41620102899634</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.0996537414483569</v>
+        <v>0.09947667197833188</v>
       </c>
       <c r="C11">
-        <v>16184.59306809018</v>
+        <v>16033.97836358685</v>
       </c>
       <c r="D11">
-        <v>15533.72106809018</v>
+        <v>15560.49836358685</v>
       </c>
       <c r="E11">
-        <v>-3733.572</v>
+        <v>-3556.18</v>
       </c>
       <c r="F11">
-        <v>1596.528</v>
+        <v>1773.92</v>
       </c>
       <c r="G11">
         <v>2247.4</v>
@@ -2195,28 +2195,28 @@
         <v>2683.5</v>
       </c>
       <c r="M11">
-        <v>80.3053584</v>
+        <v>89.22817599999999</v>
       </c>
       <c r="N11">
-        <v>2603.1946416</v>
+        <v>2594.271824</v>
       </c>
       <c r="O11">
-        <v>546.670874736</v>
+        <v>544.79708304</v>
       </c>
       <c r="P11">
-        <v>2056.523766864</v>
+        <v>2049.47474096</v>
       </c>
       <c r="Q11">
-        <v>2947.623766864</v>
+        <v>2940.57474096</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1055795730201724</v>
+        <v>0.1061144133092576</v>
       </c>
       <c r="T11">
-        <v>1.007969481746478</v>
+        <v>1.016987657383572</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2233,7 +2233,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>33.41620102899634</v>
+        <v>30.07458092609671</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2241,22 +2241,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.09947667197833188</v>
+        <v>0.09929960250830686</v>
       </c>
       <c r="C12">
-        <v>16033.97836358685</v>
+        <v>15883.45613682313</v>
       </c>
       <c r="D12">
-        <v>15560.49836358685</v>
+        <v>15587.36813682313</v>
       </c>
       <c r="E12">
-        <v>-3556.18</v>
+        <v>-3378.788</v>
       </c>
       <c r="F12">
-        <v>1773.92</v>
+        <v>1951.312</v>
       </c>
       <c r="G12">
         <v>2247.4</v>
@@ -2277,28 +2277,28 @@
         <v>2683.5</v>
       </c>
       <c r="M12">
-        <v>89.228176</v>
+        <v>98.15099360000001</v>
       </c>
       <c r="N12">
-        <v>2594.271824</v>
+        <v>2585.3490064</v>
       </c>
       <c r="O12">
-        <v>544.79708304</v>
+        <v>542.9232913439999</v>
       </c>
       <c r="P12">
-        <v>2049.47474096</v>
+        <v>2042.425715056</v>
       </c>
       <c r="Q12">
-        <v>2940.57474096</v>
+        <v>2933.525715056</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1061144133092576</v>
+        <v>0.1066612724812437</v>
       </c>
       <c r="T12">
-        <v>1.016987657383572</v>
+        <v>1.026208488652959</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2315,7 +2315,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>30.0745809260967</v>
+        <v>27.34052811463336</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2323,22 +2323,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.09929960250830686</v>
+        <v>0.09912253303828183</v>
       </c>
       <c r="C13">
-        <v>15883.45613682313</v>
+        <v>15733.02686769768</v>
       </c>
       <c r="D13">
-        <v>15587.36813682313</v>
+        <v>15614.33086769767</v>
       </c>
       <c r="E13">
-        <v>-3378.788</v>
+        <v>-3201.396</v>
       </c>
       <c r="F13">
-        <v>1951.312</v>
+        <v>2128.704</v>
       </c>
       <c r="G13">
         <v>2247.4</v>
@@ -2359,28 +2359,28 @@
         <v>2683.5</v>
       </c>
       <c r="M13">
-        <v>98.15099360000001</v>
+        <v>107.0738112</v>
       </c>
       <c r="N13">
-        <v>2585.3490064</v>
+        <v>2576.4261888</v>
       </c>
       <c r="O13">
-        <v>542.9232913439999</v>
+        <v>541.0494996480001</v>
       </c>
       <c r="P13">
-        <v>2042.425715056</v>
+        <v>2035.376689152</v>
       </c>
       <c r="Q13">
-        <v>2933.525715056</v>
+        <v>2926.476689152</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1066612724812437</v>
+        <v>0.1072205602707748</v>
       </c>
       <c r="T13">
-        <v>1.026208488652959</v>
+        <v>1.035638884269379</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2397,7 +2397,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>27.34052811463336</v>
+        <v>25.06215077174726</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2405,22 +2405,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.09912253303828183</v>
+        <v>0.09894546356825683</v>
       </c>
       <c r="C14">
-        <v>15733.02686769768</v>
+        <v>15582.69103943539</v>
       </c>
       <c r="D14">
-        <v>15614.33086769767</v>
+        <v>15641.38703943539</v>
       </c>
       <c r="E14">
-        <v>-3201.396</v>
+        <v>-3024.004</v>
       </c>
       <c r="F14">
-        <v>2128.704</v>
+        <v>2306.096</v>
       </c>
       <c r="G14">
         <v>2247.4</v>
@@ -2441,28 +2441,28 @@
         <v>2683.5</v>
       </c>
       <c r="M14">
-        <v>107.0738112</v>
+        <v>115.9966288</v>
       </c>
       <c r="N14">
-        <v>2576.4261888</v>
+        <v>2567.5033712</v>
       </c>
       <c r="O14">
-        <v>541.0494996480001</v>
+        <v>539.1757079519999</v>
       </c>
       <c r="P14">
-        <v>2035.376689152</v>
+        <v>2028.327663248</v>
       </c>
       <c r="Q14">
-        <v>2926.476689152</v>
+        <v>2919.427663248</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1072205602707748</v>
+        <v>0.1077927052508699</v>
       </c>
       <c r="T14">
-        <v>1.035638884269379</v>
+        <v>1.045286070589624</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2479,7 +2479,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>25.06215077174726</v>
+        <v>23.13429302007439</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2487,22 +2487,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.09894546356825683</v>
+        <v>0.09876839409823179</v>
       </c>
       <c r="C15">
-        <v>15582.69103943539</v>
+        <v>15432.44913861628</v>
       </c>
       <c r="D15">
-        <v>15641.38703943539</v>
+        <v>15668.53713861628</v>
       </c>
       <c r="E15">
-        <v>-3024.004</v>
+        <v>-2846.612</v>
       </c>
       <c r="F15">
-        <v>2306.096</v>
+        <v>2483.488</v>
       </c>
       <c r="G15">
         <v>2247.4</v>
@@ -2523,28 +2523,28 @@
         <v>2683.5</v>
       </c>
       <c r="M15">
-        <v>115.9966288</v>
+        <v>124.9194464</v>
       </c>
       <c r="N15">
-        <v>2567.5033712</v>
+        <v>2558.5805536</v>
       </c>
       <c r="O15">
-        <v>539.1757079519999</v>
+        <v>537.3019162559999</v>
       </c>
       <c r="P15">
-        <v>2028.327663248</v>
+        <v>2021.278637344</v>
       </c>
       <c r="Q15">
-        <v>2919.427663248</v>
+        <v>2912.378637344</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1077927052508699</v>
+        <v>0.1083781559281765</v>
       </c>
       <c r="T15">
-        <v>1.045286070589624</v>
+        <v>1.055157610080107</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2561,7 +2561,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>23.13429302007439</v>
+        <v>21.4818435186405</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2569,22 +2569,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.09876839409823179</v>
+        <v>0.09859132462820677</v>
       </c>
       <c r="C16">
-        <v>15432.44913861628</v>
+        <v>15282.30165520461</v>
       </c>
       <c r="D16">
-        <v>15668.53713861628</v>
+        <v>15695.78165520461</v>
       </c>
       <c r="E16">
-        <v>-2846.612</v>
+        <v>-2669.22</v>
       </c>
       <c r="F16">
-        <v>2483.488</v>
+        <v>2660.880000000001</v>
       </c>
       <c r="G16">
         <v>2247.4</v>
@@ -2605,28 +2605,28 @@
         <v>2683.5</v>
       </c>
       <c r="M16">
-        <v>124.9194464</v>
+        <v>133.842264</v>
       </c>
       <c r="N16">
-        <v>2558.5805536</v>
+        <v>2549.657736</v>
       </c>
       <c r="O16">
-        <v>537.3019162559999</v>
+        <v>535.42812456</v>
       </c>
       <c r="P16">
-        <v>2021.278637344</v>
+        <v>2014.22961144</v>
       </c>
       <c r="Q16">
-        <v>2912.378637344</v>
+        <v>2905.32961144</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1083781559281765</v>
+        <v>0.1089773819155374</v>
       </c>
       <c r="T16">
-        <v>1.055157610080107</v>
+        <v>1.065261421088013</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>21.4818435186405</v>
+        <v>20.0497206173978</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2651,22 +2651,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.09859132462820677</v>
+        <v>0.09841425515818174</v>
       </c>
       <c r="C17">
-        <v>15282.30165520461</v>
+        <v>15132.24908257839</v>
       </c>
       <c r="D17">
-        <v>15695.78165520461</v>
+        <v>15723.12108257839</v>
       </c>
       <c r="E17">
-        <v>-2669.22</v>
+        <v>-2491.828</v>
       </c>
       <c r="F17">
-        <v>2660.88</v>
+        <v>2838.272</v>
       </c>
       <c r="G17">
         <v>2247.4</v>
@@ -2687,28 +2687,28 @@
         <v>2683.5</v>
       </c>
       <c r="M17">
-        <v>133.842264</v>
+        <v>142.7650816</v>
       </c>
       <c r="N17">
-        <v>2549.657736</v>
+        <v>2540.7349184</v>
       </c>
       <c r="O17">
-        <v>535.42812456</v>
+        <v>533.554332864</v>
       </c>
       <c r="P17">
-        <v>2014.22961144</v>
+        <v>2007.180585536</v>
       </c>
       <c r="Q17">
-        <v>2905.32961144</v>
+        <v>2898.280585536</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1089773819155374</v>
+        <v>0.1095908751883116</v>
       </c>
       <c r="T17">
-        <v>1.065261421088013</v>
+        <v>1.075605799024679</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2725,7 +2725,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>20.04972061739781</v>
+        <v>18.79661307881044</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2733,22 +2733,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.09841425515818174</v>
+        <v>0.09823718568815672</v>
       </c>
       <c r="C18">
-        <v>15132.24908257839</v>
+        <v>14982.29191755917</v>
       </c>
       <c r="D18">
-        <v>15723.12108257839</v>
+        <v>15750.55591755917</v>
       </c>
       <c r="E18">
-        <v>-2491.828</v>
+        <v>-2314.436</v>
       </c>
       <c r="F18">
-        <v>2838.272</v>
+        <v>3015.664</v>
       </c>
       <c r="G18">
         <v>2247.4</v>
@@ -2769,28 +2769,28 @@
         <v>2683.5</v>
       </c>
       <c r="M18">
-        <v>142.7650816</v>
+        <v>151.6878992</v>
       </c>
       <c r="N18">
-        <v>2540.7349184</v>
+        <v>2531.8121008</v>
       </c>
       <c r="O18">
-        <v>533.554332864</v>
+        <v>531.680541168</v>
       </c>
       <c r="P18">
-        <v>2007.180585536</v>
+        <v>2000.131559632</v>
       </c>
       <c r="Q18">
-        <v>2898.280585536</v>
+        <v>2891.231559632</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1095908751883116</v>
+        <v>0.1102191514315141</v>
       </c>
       <c r="T18">
-        <v>1.075605799024679</v>
+        <v>1.086199439080301</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2807,7 +2807,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>18.79661307881044</v>
+        <v>17.69092995652747</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2815,22 +2815,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.09823718568815672</v>
+        <v>0.0980601162181317</v>
       </c>
       <c r="C19">
-        <v>14982.29191755917</v>
+        <v>14832.4306604421</v>
       </c>
       <c r="D19">
-        <v>15750.55591755917</v>
+        <v>15778.0866604421</v>
       </c>
       <c r="E19">
-        <v>-2314.436</v>
+        <v>-2137.044</v>
       </c>
       <c r="F19">
-        <v>3015.664</v>
+        <v>3193.056</v>
       </c>
       <c r="G19">
         <v>2247.4</v>
@@ -2851,28 +2851,28 @@
         <v>2683.5</v>
       </c>
       <c r="M19">
-        <v>151.6878992</v>
+        <v>160.6107168</v>
       </c>
       <c r="N19">
-        <v>2531.8121008</v>
+        <v>2522.8892832</v>
       </c>
       <c r="O19">
-        <v>531.680541168</v>
+        <v>529.806749472</v>
       </c>
       <c r="P19">
-        <v>2000.131559632</v>
+        <v>1993.082533728</v>
       </c>
       <c r="Q19">
-        <v>2891.231559632</v>
+        <v>2884.182533728</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1102191514315141</v>
+        <v>0.1108627514855265</v>
       </c>
       <c r="T19">
-        <v>1.086199439080301</v>
+        <v>1.097051460600694</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>17.69092995652747</v>
+        <v>16.70810051449817</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2897,22 +2897,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.09806011621813171</v>
+        <v>0.09788304674810669</v>
       </c>
       <c r="C20">
-        <v>14832.43066044209</v>
+        <v>14682.66581502636</v>
       </c>
       <c r="D20">
-        <v>15778.08666044209</v>
+        <v>15805.71381502636</v>
       </c>
       <c r="E20">
-        <v>-2137.044</v>
+        <v>-1959.652</v>
       </c>
       <c r="F20">
-        <v>3193.056</v>
+        <v>3370.448</v>
       </c>
       <c r="G20">
         <v>2247.4</v>
@@ -2933,28 +2933,28 @@
         <v>2683.5</v>
       </c>
       <c r="M20">
-        <v>160.6107168</v>
+        <v>169.5335344</v>
       </c>
       <c r="N20">
-        <v>2522.8892832</v>
+        <v>2513.9664656</v>
       </c>
       <c r="O20">
-        <v>529.806749472</v>
+        <v>527.932957776</v>
       </c>
       <c r="P20">
-        <v>1993.082533728</v>
+        <v>1986.033507824</v>
       </c>
       <c r="Q20">
-        <v>2884.182533728</v>
+        <v>2877.133507824</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1108627514855265</v>
+        <v>0.1115222428988971</v>
       </c>
       <c r="T20">
-        <v>1.097051460600694</v>
+        <v>1.108171433269739</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -2971,7 +2971,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>16.70810051449817</v>
+        <v>15.82872680320879</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2979,22 +2979,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.09788304674810669</v>
+        <v>0.09770597727808167</v>
       </c>
       <c r="C21">
-        <v>14682.66581502636</v>
+        <v>14532.99788864594</v>
       </c>
       <c r="D21">
-        <v>15805.71381502636</v>
+        <v>15833.43788864594</v>
       </c>
       <c r="E21">
-        <v>-1959.652</v>
+        <v>-1782.26</v>
       </c>
       <c r="F21">
-        <v>3370.448</v>
+        <v>3547.84</v>
       </c>
       <c r="G21">
         <v>2247.4</v>
@@ -3015,28 +3015,28 @@
         <v>2683.5</v>
       </c>
       <c r="M21">
-        <v>169.5335344</v>
+        <v>178.456352</v>
       </c>
       <c r="N21">
-        <v>2513.9664656</v>
+        <v>2505.043648</v>
       </c>
       <c r="O21">
-        <v>527.932957776</v>
+        <v>526.05916608</v>
       </c>
       <c r="P21">
-        <v>1986.033507824</v>
+        <v>1978.98448192</v>
       </c>
       <c r="Q21">
-        <v>2877.133507824</v>
+        <v>2870.08448192</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1115222428988971</v>
+        <v>0.1121982215976021</v>
       </c>
       <c r="T21">
-        <v>1.108171433269739</v>
+        <v>1.11956940525551</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3053,7 +3053,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>15.82872680320879</v>
+        <v>15.03729046304835</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3061,22 +3061,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.09770597727808167</v>
+        <v>0.09752890780805665</v>
       </c>
       <c r="C22">
-        <v>14532.99788864594</v>
+        <v>14383.42739220059</v>
       </c>
       <c r="D22">
-        <v>15833.43788864594</v>
+        <v>15861.25939220058</v>
       </c>
       <c r="E22">
-        <v>-1782.26</v>
+        <v>-1604.868</v>
       </c>
       <c r="F22">
-        <v>3547.84</v>
+        <v>3725.232</v>
       </c>
       <c r="G22">
         <v>2247.4</v>
@@ -3097,28 +3097,28 @@
         <v>2683.5</v>
       </c>
       <c r="M22">
-        <v>178.456352</v>
+        <v>187.3791696</v>
       </c>
       <c r="N22">
-        <v>2505.043648</v>
+        <v>2496.1208304</v>
       </c>
       <c r="O22">
-        <v>526.05916608</v>
+        <v>524.1853743840001</v>
       </c>
       <c r="P22">
-        <v>1978.98448192</v>
+        <v>1971.935456016</v>
       </c>
       <c r="Q22">
-        <v>2870.08448192</v>
+        <v>2863.035456016</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1121982215976021</v>
+        <v>0.1128913136810843</v>
       </c>
       <c r="T22">
-        <v>1.11956940525551</v>
+        <v>1.131255933494085</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3135,7 +3135,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>15.03729046304835</v>
+        <v>14.321229012427</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3143,22 +3143,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.09752890780805665</v>
+        <v>0.09735183833803161</v>
       </c>
       <c r="C23">
-        <v>14383.42739220059</v>
+        <v>14233.95484018729</v>
       </c>
       <c r="D23">
-        <v>15861.25939220058</v>
+        <v>15889.17884018728</v>
       </c>
       <c r="E23">
-        <v>-1604.868</v>
+        <v>-1427.476</v>
       </c>
       <c r="F23">
-        <v>3725.232</v>
+        <v>3902.624</v>
       </c>
       <c r="G23">
         <v>2247.4</v>
@@ -3179,28 +3179,28 @@
         <v>2683.5</v>
       </c>
       <c r="M23">
-        <v>187.3791696</v>
+        <v>196.3019872</v>
       </c>
       <c r="N23">
-        <v>2496.1208304</v>
+        <v>2487.1980128</v>
       </c>
       <c r="O23">
-        <v>524.1853743840001</v>
+        <v>522.3115826879999</v>
       </c>
       <c r="P23">
-        <v>1971.935456016</v>
+        <v>1964.886430112</v>
       </c>
       <c r="Q23">
-        <v>2863.035456016</v>
+        <v>2855.986430112</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1128913136810843</v>
+        <v>0.1136021773564508</v>
       </c>
       <c r="T23">
-        <v>1.131255933494085</v>
+        <v>1.143242116302881</v>
       </c>
       <c r="U23">
         <v>0.0503</v>
@@ -3217,7 +3217,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>14.32122901242701</v>
+        <v>13.67026405731668</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.09735183833803161</v>
+        <v>0.09717476886800659</v>
       </c>
       <c r="C24">
-        <v>14233.95484018729</v>
+        <v>14084.58075073193</v>
       </c>
       <c r="D24">
-        <v>15889.17884018728</v>
+        <v>15917.19675073193</v>
       </c>
       <c r="E24">
-        <v>-1427.476</v>
+        <v>-1250.084</v>
       </c>
       <c r="F24">
-        <v>3902.624</v>
+        <v>4080.016000000001</v>
       </c>
       <c r="G24">
         <v>2247.4</v>
@@ -3261,28 +3261,28 @@
         <v>2683.5</v>
       </c>
       <c r="M24">
-        <v>196.3019872</v>
+        <v>205.2248048</v>
       </c>
       <c r="N24">
-        <v>2487.1980128</v>
+        <v>2478.2751952</v>
       </c>
       <c r="O24">
-        <v>522.3115826879999</v>
+        <v>520.4377909919999</v>
       </c>
       <c r="P24">
-        <v>1964.886430112</v>
+        <v>1957.837404208</v>
       </c>
       <c r="Q24">
-        <v>2855.986430112</v>
+        <v>2848.937404208</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1136021773564508</v>
+        <v>0.1143315050233852</v>
       </c>
       <c r="T24">
-        <v>1.143242116302881</v>
+        <v>1.155539628535281</v>
       </c>
       <c r="U24">
         <v>0.0503</v>
@@ -3299,7 +3299,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>13.67026405731668</v>
+        <v>13.07590475047683</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3307,22 +3307,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.09717476886800659</v>
+        <v>0.09699769939798156</v>
       </c>
       <c r="C25">
-        <v>14084.58075073193</v>
+        <v>13935.30564562139</v>
       </c>
       <c r="D25">
-        <v>15917.19675073193</v>
+        <v>15945.31364562139</v>
       </c>
       <c r="E25">
-        <v>-1250.084</v>
+        <v>-1072.692</v>
       </c>
       <c r="F25">
-        <v>4080.016000000001</v>
+        <v>4257.408</v>
       </c>
       <c r="G25">
         <v>2247.4</v>
@@ -3343,28 +3343,28 @@
         <v>2683.5</v>
       </c>
       <c r="M25">
-        <v>205.2248048</v>
+        <v>214.1476224</v>
       </c>
       <c r="N25">
-        <v>2478.2751952</v>
+        <v>2469.3523776</v>
       </c>
       <c r="O25">
-        <v>520.4377909919999</v>
+        <v>518.563999296</v>
       </c>
       <c r="P25">
-        <v>1957.837404208</v>
+        <v>1950.788378304</v>
       </c>
       <c r="Q25">
-        <v>2848.937404208</v>
+        <v>2841.888378304</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1143315050233852</v>
+        <v>0.11508002552366</v>
       </c>
       <c r="T25">
-        <v>1.155539628535281</v>
+        <v>1.168160759510639</v>
       </c>
       <c r="U25">
         <v>0.0503</v>
@@ -3381,7 +3381,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>13.07590475047683</v>
+        <v>12.53107538587363</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3389,22 +3389,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.09699769939798156</v>
+        <v>0.09682062992795654</v>
       </c>
       <c r="C26">
-        <v>13935.30564562139</v>
+        <v>13786.13005033589</v>
       </c>
       <c r="D26">
-        <v>15945.31364562139</v>
+        <v>15973.53005033589</v>
       </c>
       <c r="E26">
-        <v>-1072.692</v>
+        <v>-895.3000000000002</v>
       </c>
       <c r="F26">
-        <v>4257.408</v>
+        <v>4434.8</v>
       </c>
       <c r="G26">
         <v>2247.4</v>
@@ -3425,28 +3425,28 @@
         <v>2683.5</v>
       </c>
       <c r="M26">
-        <v>214.1476224</v>
+        <v>223.07044</v>
       </c>
       <c r="N26">
-        <v>2469.3523776</v>
+        <v>2460.42956</v>
       </c>
       <c r="O26">
-        <v>518.563999296</v>
+        <v>516.6902076</v>
       </c>
       <c r="P26">
-        <v>1950.788378304</v>
+        <v>1943.7393524</v>
       </c>
       <c r="Q26">
-        <v>2841.888378304</v>
+        <v>2834.8393524</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.11508002552366</v>
+        <v>0.1158485065706087</v>
       </c>
       <c r="T26">
-        <v>1.168160759510639</v>
+        <v>1.181118453978673</v>
       </c>
       <c r="U26">
         <v>0.0503</v>
@@ -3463,7 +3463,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>12.53107538587363</v>
+        <v>12.02983237043868</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3471,22 +3471,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.09682062992795654</v>
+        <v>0.09664356045793152</v>
       </c>
       <c r="C27">
-        <v>13786.13005033589</v>
+        <v>13637.05449408175</v>
       </c>
       <c r="D27">
-        <v>15973.53005033589</v>
+        <v>16001.84649408174</v>
       </c>
       <c r="E27">
-        <v>-895.3000000000002</v>
+        <v>-717.9080000000004</v>
       </c>
       <c r="F27">
-        <v>4434.8</v>
+        <v>4612.192</v>
       </c>
       <c r="G27">
         <v>2247.4</v>
@@ -3507,28 +3507,28 @@
         <v>2683.5</v>
       </c>
       <c r="M27">
-        <v>223.07044</v>
+        <v>231.9932576</v>
       </c>
       <c r="N27">
-        <v>2460.42956</v>
+        <v>2451.5067424</v>
       </c>
       <c r="O27">
-        <v>516.6902076</v>
+        <v>514.816415904</v>
       </c>
       <c r="P27">
-        <v>1943.7393524</v>
+        <v>1936.690326496</v>
       </c>
       <c r="Q27">
-        <v>2834.8393524</v>
+        <v>2827.790326496</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1158485065706087</v>
+        <v>0.1166377573755831</v>
       </c>
       <c r="T27">
-        <v>1.181118453978673</v>
+        <v>1.194426356405303</v>
       </c>
       <c r="U27">
         <v>0.0503</v>
@@ -3545,7 +3545,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>12.02983237043868</v>
+        <v>11.5671465100372</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3553,22 +3553,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.09664356045793152</v>
+        <v>0.09646649098790652</v>
       </c>
       <c r="C28">
-        <v>13637.05449408175</v>
+        <v>13488.07950982446</v>
       </c>
       <c r="D28">
-        <v>16001.84649408174</v>
+        <v>16030.26350982446</v>
       </c>
       <c r="E28">
-        <v>-717.9080000000004</v>
+        <v>-540.5159999999996</v>
       </c>
       <c r="F28">
-        <v>4612.192</v>
+        <v>4789.584000000001</v>
       </c>
       <c r="G28">
         <v>2247.4</v>
@@ -3589,28 +3589,28 @@
         <v>2683.5</v>
       </c>
       <c r="M28">
-        <v>231.9932576</v>
+        <v>240.9160752</v>
       </c>
       <c r="N28">
-        <v>2451.5067424</v>
+        <v>2442.5839248</v>
       </c>
       <c r="O28">
-        <v>514.816415904</v>
+        <v>512.942624208</v>
       </c>
       <c r="P28">
-        <v>1936.690326496</v>
+        <v>1929.641300592</v>
       </c>
       <c r="Q28">
-        <v>2827.790326496</v>
+        <v>2820.741300592</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1166377573755831</v>
+        <v>0.1174486314902829</v>
       </c>
       <c r="T28">
-        <v>1.194426356405303</v>
+        <v>1.208098858898416</v>
       </c>
       <c r="U28">
         <v>0.0503</v>
@@ -3627,7 +3627,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>11.5671465100372</v>
+        <v>11.13873367633211</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3635,22 +3635,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.09646649098790652</v>
+        <v>0.09628942151788147</v>
       </c>
       <c r="C29">
-        <v>13488.07950982446</v>
+        <v>13339.20563432217</v>
       </c>
       <c r="D29">
-        <v>16030.26350982446</v>
+        <v>16058.78163432217</v>
       </c>
       <c r="E29">
-        <v>-540.5159999999996</v>
+        <v>-363.1239999999998</v>
       </c>
       <c r="F29">
-        <v>4789.584000000001</v>
+        <v>4966.976000000001</v>
       </c>
       <c r="G29">
         <v>2247.4</v>
@@ -3671,28 +3671,28 @@
         <v>2683.5</v>
       </c>
       <c r="M29">
-        <v>240.9160752</v>
+        <v>249.8388928</v>
       </c>
       <c r="N29">
-        <v>2442.5839248</v>
+        <v>2433.6611072</v>
       </c>
       <c r="O29">
-        <v>512.942624208</v>
+        <v>511.068832512</v>
       </c>
       <c r="P29">
-        <v>1929.641300592</v>
+        <v>1922.592274688</v>
       </c>
       <c r="Q29">
-        <v>2820.741300592</v>
+        <v>2813.692274688</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1174486314902829</v>
+        <v>0.1182820298859465</v>
       </c>
       <c r="T29">
-        <v>1.208098858898416</v>
+        <v>1.222151153127449</v>
       </c>
       <c r="U29">
         <v>0.0503</v>
@@ -3709,7 +3709,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>11.13873367633211</v>
+        <v>10.74092175932025</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3717,22 +3717,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.09628942151788147</v>
+        <v>0.09611235204785644</v>
       </c>
       <c r="C30">
-        <v>13339.20563432217</v>
+        <v>13190.43340815941</v>
       </c>
       <c r="D30">
-        <v>16058.78163432217</v>
+        <v>16087.40140815941</v>
       </c>
       <c r="E30">
-        <v>-363.1239999999998</v>
+        <v>-185.732</v>
       </c>
       <c r="F30">
-        <v>4966.976000000001</v>
+        <v>5144.368</v>
       </c>
       <c r="G30">
         <v>2247.4</v>
@@ -3753,28 +3753,28 @@
         <v>2683.5</v>
       </c>
       <c r="M30">
-        <v>249.8388928</v>
+        <v>258.7617104</v>
       </c>
       <c r="N30">
-        <v>2433.6611072</v>
+        <v>2424.7382896</v>
       </c>
       <c r="O30">
-        <v>511.068832512</v>
+        <v>509.195040816</v>
       </c>
       <c r="P30">
-        <v>1922.592274688</v>
+        <v>1915.543248784</v>
       </c>
       <c r="Q30">
-        <v>2813.692274688</v>
+        <v>2806.643248784</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1182820298859465</v>
+        <v>0.1191389042927556</v>
       </c>
       <c r="T30">
-        <v>1.222151153127449</v>
+        <v>1.236599286630538</v>
       </c>
       <c r="U30">
         <v>0.0503</v>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>10.74092175932025</v>
+        <v>10.3705451469299</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3799,22 +3799,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.09611235204785644</v>
+        <v>0.09593528257783143</v>
       </c>
       <c r="C31">
-        <v>13190.43340815941</v>
+        <v>13041.76337578129</v>
       </c>
       <c r="D31">
-        <v>16087.40140815941</v>
+        <v>16116.12337578128</v>
       </c>
       <c r="E31">
-        <v>-185.7320000000009</v>
+        <v>-8.340000000000146</v>
       </c>
       <c r="F31">
-        <v>5144.367999999999</v>
+        <v>5321.76</v>
       </c>
       <c r="G31">
         <v>2247.4</v>
@@ -3835,28 +3835,28 @@
         <v>2683.5</v>
       </c>
       <c r="M31">
-        <v>258.7617104</v>
+        <v>267.684528</v>
       </c>
       <c r="N31">
-        <v>2424.7382896</v>
+        <v>2415.815472</v>
       </c>
       <c r="O31">
-        <v>509.195040816</v>
+        <v>507.32124912</v>
       </c>
       <c r="P31">
-        <v>1915.543248784</v>
+        <v>1908.49422288</v>
       </c>
       <c r="Q31">
-        <v>2806.643248784</v>
+        <v>2799.59422288</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1191389042927556</v>
+        <v>0.1200202608254735</v>
       </c>
       <c r="T31">
-        <v>1.236599286630538</v>
+        <v>1.251460223948002</v>
       </c>
       <c r="U31">
         <v>0.0503</v>
@@ -3873,7 +3873,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>10.3705451469299</v>
+        <v>10.0248603086989</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3881,22 +3881,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.09593528257783143</v>
+        <v>0.09575821310780641</v>
       </c>
       <c r="C32">
-        <v>13041.76337578129</v>
+        <v>12893.19608552802</v>
       </c>
       <c r="D32">
-        <v>16116.12337578128</v>
+        <v>16144.94808552802</v>
       </c>
       <c r="E32">
-        <v>-8.340000000000146</v>
+        <v>169.0519999999997</v>
       </c>
       <c r="F32">
-        <v>5321.76</v>
+        <v>5499.152</v>
       </c>
       <c r="G32">
         <v>2247.4</v>
@@ -3917,28 +3917,28 @@
         <v>2683.5</v>
       </c>
       <c r="M32">
-        <v>267.684528</v>
+        <v>276.6073456</v>
       </c>
       <c r="N32">
-        <v>2415.815472</v>
+        <v>2406.8926544</v>
       </c>
       <c r="O32">
-        <v>507.32124912</v>
+        <v>505.447457424</v>
       </c>
       <c r="P32">
-        <v>1908.49422288</v>
+        <v>1901.445196976</v>
       </c>
       <c r="Q32">
-        <v>2799.59422288</v>
+        <v>2792.545196976</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1200202608254735</v>
+        <v>0.1209271639243571</v>
       </c>
       <c r="T32">
-        <v>1.251460223948002</v>
+        <v>1.26675191307177</v>
       </c>
       <c r="U32">
         <v>0.0503</v>
@@ -3955,7 +3955,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>10.0248603086989</v>
+        <v>9.701477718095713</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3963,22 +3963,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.09575821310780641</v>
+        <v>0.09558114363778138</v>
       </c>
       <c r="C33">
-        <v>12893.19608552802</v>
+        <v>12744.73208966983</v>
       </c>
       <c r="D33">
-        <v>16144.94808552802</v>
+        <v>16173.87608966983</v>
       </c>
       <c r="E33">
-        <v>169.0519999999997</v>
+        <v>346.4440000000004</v>
       </c>
       <c r="F33">
-        <v>5499.152</v>
+        <v>5676.544000000001</v>
       </c>
       <c r="G33">
         <v>2247.4</v>
@@ -3999,28 +3999,28 @@
         <v>2683.5</v>
       </c>
       <c r="M33">
-        <v>276.6073456</v>
+        <v>285.5301632</v>
       </c>
       <c r="N33">
-        <v>2406.8926544</v>
+        <v>2397.9698368</v>
       </c>
       <c r="O33">
-        <v>505.447457424</v>
+        <v>503.573665728</v>
       </c>
       <c r="P33">
-        <v>1901.445196976</v>
+        <v>1894.396171072</v>
       </c>
       <c r="Q33">
-        <v>2792.545196976</v>
+        <v>2785.496171072</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1209271639243571</v>
+        <v>0.1218607406437962</v>
       </c>
       <c r="T33">
-        <v>1.26675191307177</v>
+        <v>1.282493357758001</v>
       </c>
       <c r="U33">
         <v>0.0503</v>
@@ -4037,7 +4037,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>9.701477718095713</v>
+        <v>9.398306539405221</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4045,22 +4045,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.09558114363778138</v>
+        <v>0.09540407416775636</v>
       </c>
       <c r="C34">
-        <v>12744.73208966983</v>
+        <v>12596.37194444218</v>
       </c>
       <c r="D34">
-        <v>16173.87608966983</v>
+        <v>16202.90794444218</v>
       </c>
       <c r="E34">
-        <v>346.4440000000004</v>
+        <v>523.8360000000002</v>
       </c>
       <c r="F34">
-        <v>5676.544000000001</v>
+        <v>5853.936000000001</v>
       </c>
       <c r="G34">
         <v>2247.4</v>
@@ -4081,28 +4081,28 @@
         <v>2683.5</v>
       </c>
       <c r="M34">
-        <v>285.5301632</v>
+        <v>294.4529808</v>
       </c>
       <c r="N34">
-        <v>2397.9698368</v>
+        <v>2389.0470192</v>
       </c>
       <c r="O34">
-        <v>503.573665728</v>
+        <v>501.6998740319999</v>
       </c>
       <c r="P34">
-        <v>1894.396171072</v>
+        <v>1887.347145168</v>
       </c>
       <c r="Q34">
-        <v>2785.496171072</v>
+        <v>2778.447145168</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1218607406437962</v>
+        <v>0.1228221853250095</v>
       </c>
       <c r="T34">
-        <v>1.282493357758001</v>
+        <v>1.298704696315462</v>
       </c>
       <c r="U34">
         <v>0.0503</v>
@@ -4119,7 +4119,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>9.398306539405221</v>
+        <v>9.113509371544454</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4127,22 +4127,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.09540407416775636</v>
+        <v>0.09522700469773135</v>
       </c>
       <c r="C35">
-        <v>12596.37194444218</v>
+        <v>12448.11621008145</v>
       </c>
       <c r="D35">
-        <v>16202.90794444218</v>
+        <v>16232.04421008145</v>
       </c>
       <c r="E35">
-        <v>523.8360000000002</v>
+        <v>701.2280000000001</v>
       </c>
       <c r="F35">
-        <v>5853.936000000001</v>
+        <v>6031.328</v>
       </c>
       <c r="G35">
         <v>2247.4</v>
@@ -4163,28 +4163,28 @@
         <v>2683.5</v>
       </c>
       <c r="M35">
-        <v>294.4529808</v>
+        <v>303.3757984</v>
       </c>
       <c r="N35">
-        <v>2389.0470192</v>
+        <v>2380.1242016</v>
       </c>
       <c r="O35">
-        <v>501.6998740319999</v>
+        <v>499.826082336</v>
       </c>
       <c r="P35">
-        <v>1887.347145168</v>
+        <v>1880.298119264</v>
       </c>
       <c r="Q35">
-        <v>2778.447145168</v>
+        <v>2771.398119264</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1228221853250095</v>
+        <v>0.1238127646935324</v>
       </c>
       <c r="T35">
-        <v>1.298704696315462</v>
+        <v>1.315407287556484</v>
       </c>
       <c r="U35">
         <v>0.0503</v>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>9.113509371544454</v>
+        <v>8.845464978263738</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4209,22 +4209,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.09522700469773135</v>
+        <v>0.09546468522770632</v>
       </c>
       <c r="C36">
-        <v>12448.11621008145</v>
+        <v>12231.63858621965</v>
       </c>
       <c r="D36">
-        <v>16232.04421008145</v>
+        <v>16192.95858621965</v>
       </c>
       <c r="E36">
-        <v>701.2280000000001</v>
+        <v>878.6200000000008</v>
       </c>
       <c r="F36">
-        <v>6031.328</v>
+        <v>6208.720000000001</v>
       </c>
       <c r="G36">
         <v>2247.4</v>
@@ -4245,45 +4245,45 @@
         <v>2683.5</v>
       </c>
       <c r="M36">
-        <v>303.3757984</v>
+        <v>321.6116960000001</v>
       </c>
       <c r="N36">
-        <v>2380.1242016</v>
+        <v>2361.888304</v>
       </c>
       <c r="O36">
-        <v>499.826082336</v>
+        <v>495.99654384</v>
       </c>
       <c r="P36">
-        <v>1880.298119264</v>
+        <v>1865.89176016</v>
       </c>
       <c r="Q36">
-        <v>2771.398119264</v>
+        <v>2756.99176016</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1238127646935324</v>
+        <v>0.1248338234272405</v>
       </c>
       <c r="T36">
-        <v>1.315407287556484</v>
+        <v>1.332623804681844</v>
       </c>
       <c r="U36">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V36">
         <v>0.21</v>
       </c>
       <c r="W36">
-        <v>0.039737</v>
+        <v>0.040922</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y36">
-        <v>8.845464978263738</v>
+        <v>8.343912965155345</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.09546468522770632</v>
+        <v>0.09529946575768128</v>
       </c>
       <c r="C37">
-        <v>12231.63858621965</v>
+        <v>12081.39629643743</v>
       </c>
       <c r="D37">
-        <v>16192.95858621965</v>
+        <v>16220.10829643743</v>
       </c>
       <c r="E37">
-        <v>878.6200000000008</v>
+        <v>1056.012000000001</v>
       </c>
       <c r="F37">
-        <v>6208.720000000001</v>
+        <v>6386.112000000001</v>
       </c>
       <c r="G37">
         <v>2247.4</v>
@@ -4327,28 +4327,28 @@
         <v>2683.5</v>
       </c>
       <c r="M37">
-        <v>321.6116960000001</v>
+        <v>330.8006016</v>
       </c>
       <c r="N37">
-        <v>2361.888304</v>
+        <v>2352.6993984</v>
       </c>
       <c r="O37">
-        <v>495.99654384</v>
+        <v>494.066873664</v>
       </c>
       <c r="P37">
-        <v>1865.89176016</v>
+        <v>1858.632524736</v>
       </c>
       <c r="Q37">
-        <v>2756.99176016</v>
+        <v>2749.732524736</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1248338234272405</v>
+        <v>0.125886790246377</v>
       </c>
       <c r="T37">
-        <v>1.332623804681844</v>
+        <v>1.350378337967372</v>
       </c>
       <c r="U37">
         <v>0.0518</v>
@@ -4365,7 +4365,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>8.343912965155345</v>
+        <v>8.112137605012142</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4373,22 +4373,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.09529946575768129</v>
+        <v>0.09513424628765628</v>
       </c>
       <c r="C38">
-        <v>12081.39629643743</v>
+        <v>11931.2451999596</v>
       </c>
       <c r="D38">
-        <v>16220.10829643743</v>
+        <v>16247.3491999596</v>
       </c>
       <c r="E38">
-        <v>1056.012</v>
+        <v>1233.404</v>
       </c>
       <c r="F38">
-        <v>6386.112</v>
+        <v>6563.504</v>
       </c>
       <c r="G38">
         <v>2247.4</v>
@@ -4409,28 +4409,28 @@
         <v>2683.5</v>
       </c>
       <c r="M38">
-        <v>330.8006016</v>
+        <v>339.9895072</v>
       </c>
       <c r="N38">
-        <v>2352.6993984</v>
+        <v>2343.5104928</v>
       </c>
       <c r="O38">
-        <v>494.066873664</v>
+        <v>492.137203488</v>
       </c>
       <c r="P38">
-        <v>1858.632524736</v>
+        <v>1851.373289312</v>
       </c>
       <c r="Q38">
-        <v>2749.732524736</v>
+        <v>2742.473289312</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.125886790246377</v>
+        <v>0.1269731845835814</v>
       </c>
       <c r="T38">
-        <v>1.350378337967372</v>
+        <v>1.368696507230218</v>
       </c>
       <c r="U38">
         <v>0.0518</v>
@@ -4447,7 +4447,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>8.112137605012144</v>
+        <v>7.892890642714518</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4455,22 +4455,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.09513424628765628</v>
+        <v>0.09496902681763127</v>
       </c>
       <c r="C39">
-        <v>11931.2451999596</v>
+        <v>11781.18575702364</v>
       </c>
       <c r="D39">
-        <v>16247.3491999596</v>
+        <v>16274.68175702364</v>
       </c>
       <c r="E39">
-        <v>1233.404</v>
+        <v>1410.796</v>
       </c>
       <c r="F39">
-        <v>6563.504</v>
+        <v>6740.896000000001</v>
       </c>
       <c r="G39">
         <v>2247.4</v>
@@ -4491,28 +4491,28 @@
         <v>2683.5</v>
       </c>
       <c r="M39">
-        <v>339.9895072</v>
+        <v>349.1784128</v>
       </c>
       <c r="N39">
-        <v>2343.5104928</v>
+        <v>2334.3215872</v>
       </c>
       <c r="O39">
-        <v>492.137203488</v>
+        <v>490.207533312</v>
       </c>
       <c r="P39">
-        <v>1851.373289312</v>
+        <v>1844.114053888</v>
       </c>
       <c r="Q39">
-        <v>2742.473289312</v>
+        <v>2735.214053888</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1269731845835814</v>
+        <v>0.1280946238994053</v>
       </c>
       <c r="T39">
-        <v>1.368696507230218</v>
+        <v>1.387605585178962</v>
       </c>
       <c r="U39">
         <v>0.0518</v>
@@ -4529,7 +4529,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>7.892890642714518</v>
+        <v>7.685182994222029</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4537,22 +4537,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.09496902681763127</v>
+        <v>0.09480380734760624</v>
       </c>
       <c r="C40">
-        <v>11781.18575702364</v>
+        <v>11631.21843096919</v>
       </c>
       <c r="D40">
-        <v>16274.68175702364</v>
+        <v>16302.10643096919</v>
       </c>
       <c r="E40">
-        <v>1410.796</v>
+        <v>1588.188</v>
       </c>
       <c r="F40">
-        <v>6740.896000000001</v>
+        <v>6918.288</v>
       </c>
       <c r="G40">
         <v>2247.4</v>
@@ -4573,28 +4573,28 @@
         <v>2683.5</v>
       </c>
       <c r="M40">
-        <v>349.1784128</v>
+        <v>358.3673184</v>
       </c>
       <c r="N40">
-        <v>2334.3215872</v>
+        <v>2325.1326816</v>
       </c>
       <c r="O40">
-        <v>490.207533312</v>
+        <v>488.277863136</v>
       </c>
       <c r="P40">
-        <v>1844.114053888</v>
+        <v>1836.854818464</v>
       </c>
       <c r="Q40">
-        <v>2735.214053888</v>
+        <v>2727.954818464</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1280946238994053</v>
+        <v>0.1292528317173873</v>
       </c>
       <c r="T40">
-        <v>1.387605585178962</v>
+        <v>1.407134632896518</v>
       </c>
       <c r="U40">
         <v>0.0518</v>
@@ -4611,7 +4611,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>7.685182994222029</v>
+        <v>7.488127020011209</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4619,22 +4619,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.09480380734760624</v>
+        <v>0.09463858787758121</v>
       </c>
       <c r="C41">
-        <v>11631.21843096919</v>
+        <v>11481.34368826431</v>
       </c>
       <c r="D41">
-        <v>16302.10643096919</v>
+        <v>16329.62368826432</v>
       </c>
       <c r="E41">
-        <v>1588.188</v>
+        <v>1765.58</v>
       </c>
       <c r="F41">
-        <v>6918.288</v>
+        <v>7095.68</v>
       </c>
       <c r="G41">
         <v>2247.4</v>
@@ -4655,28 +4655,28 @@
         <v>2683.5</v>
       </c>
       <c r="M41">
-        <v>358.3673184</v>
+        <v>367.556224</v>
       </c>
       <c r="N41">
-        <v>2325.1326816</v>
+        <v>2315.943776</v>
       </c>
       <c r="O41">
-        <v>488.277863136</v>
+        <v>486.34819296</v>
       </c>
       <c r="P41">
-        <v>1836.854818464</v>
+        <v>1829.59558304</v>
       </c>
       <c r="Q41">
-        <v>2727.954818464</v>
+        <v>2720.69558304</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1292528317173873</v>
+        <v>0.1304496464626353</v>
       </c>
       <c r="T41">
-        <v>1.407134632896518</v>
+        <v>1.427314648871326</v>
       </c>
       <c r="U41">
         <v>0.0518</v>
@@ -4693,7 +4693,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>7.488127020011209</v>
+        <v>7.300923844510929</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4701,22 +4701,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.09463858787758121</v>
+        <v>0.09447336840755619</v>
       </c>
       <c r="C42">
-        <v>11481.34368826431</v>
+        <v>11331.5619985319</v>
       </c>
       <c r="D42">
-        <v>16329.62368826432</v>
+        <v>16357.23399853189</v>
       </c>
       <c r="E42">
-        <v>1765.58</v>
+        <v>1942.972000000001</v>
       </c>
       <c r="F42">
-        <v>7095.68</v>
+        <v>7273.072000000001</v>
       </c>
       <c r="G42">
         <v>2247.4</v>
@@ -4737,28 +4737,28 @@
         <v>2683.5</v>
       </c>
       <c r="M42">
-        <v>367.556224</v>
+        <v>376.7451296</v>
       </c>
       <c r="N42">
-        <v>2315.943776</v>
+        <v>2306.7548704</v>
       </c>
       <c r="O42">
-        <v>486.34819296</v>
+        <v>484.418522784</v>
       </c>
       <c r="P42">
-        <v>1829.59558304</v>
+        <v>1822.336347616</v>
       </c>
       <c r="Q42">
-        <v>2720.69558304</v>
+        <v>2713.436347616</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1304496464626353</v>
+        <v>0.1316870311992478</v>
       </c>
       <c r="T42">
-        <v>1.427314648871326</v>
+        <v>1.448178733184262</v>
       </c>
       <c r="U42">
         <v>0.0518</v>
@@ -4775,7 +4775,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>7.300923844510929</v>
+        <v>7.122852531230174</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4783,22 +4783,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.09447336840755619</v>
+        <v>0.09430814893753116</v>
       </c>
       <c r="C43">
-        <v>11331.5619985319</v>
+        <v>11181.87383457637</v>
       </c>
       <c r="D43">
-        <v>16357.23399853189</v>
+        <v>16384.93783457637</v>
       </c>
       <c r="E43">
-        <v>1942.972000000001</v>
+        <v>2120.364</v>
       </c>
       <c r="F43">
-        <v>7273.072000000001</v>
+        <v>7450.464000000001</v>
       </c>
       <c r="G43">
         <v>2247.4</v>
@@ -4819,28 +4819,28 @@
         <v>2683.5</v>
       </c>
       <c r="M43">
-        <v>376.7451296</v>
+        <v>385.9340352</v>
       </c>
       <c r="N43">
-        <v>2306.7548704</v>
+        <v>2297.5659648</v>
       </c>
       <c r="O43">
-        <v>484.418522784</v>
+        <v>482.488852608</v>
       </c>
       <c r="P43">
-        <v>1822.336347616</v>
+        <v>1815.077112192</v>
       </c>
       <c r="Q43">
-        <v>2713.436347616</v>
+        <v>2706.177112192</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1316870311992478</v>
+        <v>0.1329670843750537</v>
       </c>
       <c r="T43">
-        <v>1.448178733184262</v>
+        <v>1.469762268680403</v>
       </c>
       <c r="U43">
         <v>0.0518</v>
@@ -4857,7 +4857,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>7.122852531230174</v>
+        <v>6.953260804296122</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4865,22 +4865,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.09430814893753117</v>
+        <v>0.09414292946750613</v>
       </c>
       <c r="C44">
-        <v>11181.87383457637</v>
+        <v>11032.27967241072</v>
       </c>
       <c r="D44">
-        <v>16384.93783457637</v>
+        <v>16412.73567241072</v>
       </c>
       <c r="E44">
-        <v>2120.364</v>
+        <v>2297.755999999999</v>
       </c>
       <c r="F44">
-        <v>7450.464</v>
+        <v>7627.856</v>
       </c>
       <c r="G44">
         <v>2247.4</v>
@@ -4901,28 +4901,28 @@
         <v>2683.5</v>
       </c>
       <c r="M44">
-        <v>385.9340352</v>
+        <v>395.1229408</v>
       </c>
       <c r="N44">
-        <v>2297.5659648</v>
+        <v>2288.3770592</v>
       </c>
       <c r="O44">
-        <v>482.488852608</v>
+        <v>480.559182432</v>
       </c>
       <c r="P44">
-        <v>1815.077112192</v>
+        <v>1807.817876768</v>
       </c>
       <c r="Q44">
-        <v>2706.177112192</v>
+        <v>2698.917876768</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1329670843750537</v>
+        <v>0.1342920516973792</v>
       </c>
       <c r="T44">
-        <v>1.469762268680403</v>
+        <v>1.492103121211497</v>
       </c>
       <c r="U44">
         <v>0.0518</v>
@@ -4939,7 +4939,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>6.953260804296123</v>
+        <v>6.79155706466133</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4947,22 +4947,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.09414292946750613</v>
+        <v>0.09456862999748114</v>
       </c>
       <c r="C45">
-        <v>11032.27967241072</v>
+        <v>10783.45516870618</v>
       </c>
       <c r="D45">
-        <v>16412.73567241072</v>
+        <v>16341.30316870618</v>
       </c>
       <c r="E45">
-        <v>2297.755999999999</v>
+        <v>2475.148</v>
       </c>
       <c r="F45">
-        <v>7627.856</v>
+        <v>7805.248000000001</v>
       </c>
       <c r="G45">
         <v>2247.4</v>
@@ -4983,45 +4983,45 @@
         <v>2683.5</v>
       </c>
       <c r="M45">
-        <v>395.1229408</v>
+        <v>417.580768</v>
       </c>
       <c r="N45">
-        <v>2288.3770592</v>
+        <v>2265.919232</v>
       </c>
       <c r="O45">
-        <v>480.559182432</v>
+        <v>475.84303872</v>
       </c>
       <c r="P45">
-        <v>1807.817876768</v>
+        <v>1790.07619328</v>
       </c>
       <c r="Q45">
-        <v>2698.917876768</v>
+        <v>2681.17619328</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1342920516973792</v>
+        <v>0.1356643392812163</v>
       </c>
       <c r="T45">
-        <v>1.492103121211497</v>
+        <v>1.515241861332987</v>
       </c>
       <c r="U45">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V45">
         <v>0.21</v>
       </c>
       <c r="W45">
-        <v>0.040922</v>
+        <v>0.042265</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y45">
-        <v>6.79155706466133</v>
+        <v>6.426301701710554</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5029,22 +5029,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.09456862999748114</v>
+        <v>0.09441684052745611</v>
       </c>
       <c r="C46">
-        <v>10783.45516870618</v>
+        <v>10631.46198784791</v>
       </c>
       <c r="D46">
-        <v>16341.30316870618</v>
+        <v>16366.70198784791</v>
       </c>
       <c r="E46">
-        <v>2475.148</v>
+        <v>2652.54</v>
       </c>
       <c r="F46">
-        <v>7805.248000000001</v>
+        <v>7982.64</v>
       </c>
       <c r="G46">
         <v>2247.4</v>
@@ -5065,28 +5065,28 @@
         <v>2683.5</v>
       </c>
       <c r="M46">
-        <v>417.580768</v>
+        <v>427.07124</v>
       </c>
       <c r="N46">
-        <v>2265.919232</v>
+        <v>2256.42876</v>
       </c>
       <c r="O46">
-        <v>475.84303872</v>
+        <v>473.8500395999999</v>
       </c>
       <c r="P46">
-        <v>1790.07619328</v>
+        <v>1782.5787204</v>
       </c>
       <c r="Q46">
-        <v>2681.17619328</v>
+        <v>2673.6787204</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1356643392812163</v>
+        <v>0.1370865282317384</v>
       </c>
       <c r="T46">
-        <v>1.515241861332987</v>
+        <v>1.539222010186167</v>
       </c>
       <c r="U46">
         <v>0.0535</v>
@@ -5103,7 +5103,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>6.426301701710554</v>
+        <v>6.283494997228097</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5111,22 +5111,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.09441684052745611</v>
+        <v>0.09426505105743109</v>
       </c>
       <c r="C47">
-        <v>10631.46198784791</v>
+        <v>10479.54788320876</v>
       </c>
       <c r="D47">
-        <v>16366.70198784791</v>
+        <v>16392.17988320876</v>
       </c>
       <c r="E47">
-        <v>2652.54</v>
+        <v>2829.932000000001</v>
       </c>
       <c r="F47">
-        <v>7982.64</v>
+        <v>8160.032000000001</v>
       </c>
       <c r="G47">
         <v>2247.4</v>
@@ -5147,28 +5147,28 @@
         <v>2683.5</v>
       </c>
       <c r="M47">
-        <v>427.07124</v>
+        <v>436.5617120000001</v>
       </c>
       <c r="N47">
-        <v>2256.42876</v>
+        <v>2246.938288</v>
       </c>
       <c r="O47">
-        <v>473.8500395999999</v>
+        <v>471.85704048</v>
       </c>
       <c r="P47">
-        <v>1782.5787204</v>
+        <v>1775.08124752</v>
       </c>
       <c r="Q47">
-        <v>2673.6787204</v>
+        <v>2666.18124752</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1370865282317384</v>
+        <v>0.1385613908470946</v>
       </c>
       <c r="T47">
-        <v>1.539222010186167</v>
+        <v>1.564090312700577</v>
       </c>
       <c r="U47">
         <v>0.0535</v>
@@ -5185,7 +5185,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>6.283494997228097</v>
+        <v>6.14689727989705</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5193,22 +5193,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.09426505105743109</v>
+        <v>0.09411326158740607</v>
       </c>
       <c r="C48">
-        <v>10479.54788320876</v>
+        <v>10327.71322465619</v>
       </c>
       <c r="D48">
-        <v>16392.17988320876</v>
+        <v>16417.73722465619</v>
       </c>
       <c r="E48">
-        <v>2829.932000000001</v>
+        <v>3007.324000000001</v>
       </c>
       <c r="F48">
-        <v>8160.032000000001</v>
+        <v>8337.424000000001</v>
       </c>
       <c r="G48">
         <v>2247.4</v>
@@ -5229,28 +5229,28 @@
         <v>2683.5</v>
       </c>
       <c r="M48">
-        <v>436.5617120000001</v>
+        <v>446.052184</v>
       </c>
       <c r="N48">
-        <v>2246.938288</v>
+        <v>2237.447816</v>
       </c>
       <c r="O48">
-        <v>471.85704048</v>
+        <v>469.8640413599999</v>
       </c>
       <c r="P48">
-        <v>1775.08124752</v>
+        <v>1767.58377464</v>
       </c>
       <c r="Q48">
-        <v>2666.18124752</v>
+        <v>2658.68377464</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1385613908470946</v>
+        <v>0.1400919086554831</v>
       </c>
       <c r="T48">
-        <v>1.564090312700577</v>
+        <v>1.589897041724964</v>
       </c>
       <c r="U48">
         <v>0.0535</v>
@@ -5267,7 +5267,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>6.14689727989705</v>
+        <v>6.016112231388603</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5275,22 +5275,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.09411326158740607</v>
+        <v>0.09396147211738104</v>
       </c>
       <c r="C49">
-        <v>10327.71322465619</v>
+        <v>10175.95838436792</v>
       </c>
       <c r="D49">
-        <v>16417.73722465619</v>
+        <v>16443.37438436792</v>
       </c>
       <c r="E49">
-        <v>3007.324000000001</v>
+        <v>3184.716</v>
       </c>
       <c r="F49">
-        <v>8337.424000000001</v>
+        <v>8514.816000000001</v>
       </c>
       <c r="G49">
         <v>2247.4</v>
@@ -5311,28 +5311,28 @@
         <v>2683.5</v>
       </c>
       <c r="M49">
-        <v>446.052184</v>
+        <v>455.542656</v>
       </c>
       <c r="N49">
-        <v>2237.447816</v>
+        <v>2227.957344</v>
       </c>
       <c r="O49">
-        <v>469.8640413599999</v>
+        <v>467.87104224</v>
       </c>
       <c r="P49">
-        <v>1767.58377464</v>
+        <v>1760.08630176</v>
       </c>
       <c r="Q49">
-        <v>2658.68377464</v>
+        <v>2651.18630176</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1400919086554831</v>
+        <v>0.1416812925334251</v>
       </c>
       <c r="T49">
-        <v>1.589897041724964</v>
+        <v>1.616696337250289</v>
       </c>
       <c r="U49">
         <v>0.0535</v>
@@ -5349,7 +5349,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>6.016112231388603</v>
+        <v>5.890776559901341</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.09396147211738103</v>
+        <v>0.09380968264735601</v>
       </c>
       <c r="C50">
-        <v>10175.95838436792</v>
+        <v>10024.28373685001</v>
       </c>
       <c r="D50">
-        <v>16443.37438436792</v>
+        <v>16469.09173685</v>
       </c>
       <c r="E50">
-        <v>3184.716</v>
+        <v>3362.108</v>
       </c>
       <c r="F50">
-        <v>8514.816000000001</v>
+        <v>8692.208000000001</v>
       </c>
       <c r="G50">
         <v>2247.4</v>
@@ -5393,28 +5393,28 @@
         <v>2683.5</v>
       </c>
       <c r="M50">
-        <v>455.542656</v>
+        <v>465.033128</v>
       </c>
       <c r="N50">
-        <v>2227.957344</v>
+        <v>2218.466872</v>
       </c>
       <c r="O50">
-        <v>467.87104224</v>
+        <v>465.87804312</v>
       </c>
       <c r="P50">
-        <v>1760.08630176</v>
+        <v>1752.58882888</v>
       </c>
       <c r="Q50">
-        <v>2651.18630176</v>
+        <v>2643.68882888</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.141681292533425</v>
+        <v>0.1433330051908941</v>
       </c>
       <c r="T50">
-        <v>1.616696337250288</v>
+        <v>1.644546585541313</v>
       </c>
       <c r="U50">
         <v>0.0535</v>
@@ -5431,7 +5431,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>5.890776559901341</v>
+        <v>5.770556630107436</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5439,22 +5439,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.09380968264735601</v>
+        <v>0.09365789317733099</v>
       </c>
       <c r="C51">
-        <v>10024.28373685001</v>
+        <v>9872.68965895508</v>
       </c>
       <c r="D51">
-        <v>16469.09173685</v>
+        <v>16494.88965895508</v>
       </c>
       <c r="E51">
-        <v>3362.108</v>
+        <v>3539.5</v>
       </c>
       <c r="F51">
-        <v>8692.208000000001</v>
+        <v>8869.6</v>
       </c>
       <c r="G51">
         <v>2247.4</v>
@@ -5475,28 +5475,28 @@
         <v>2683.5</v>
       </c>
       <c r="M51">
-        <v>465.033128</v>
+        <v>474.5236</v>
       </c>
       <c r="N51">
-        <v>2218.466872</v>
+        <v>2208.9764</v>
       </c>
       <c r="O51">
-        <v>465.87804312</v>
+        <v>463.885044</v>
       </c>
       <c r="P51">
-        <v>1752.58882888</v>
+        <v>1745.091356</v>
       </c>
       <c r="Q51">
-        <v>2643.68882888</v>
+        <v>2636.191356</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1433330051908941</v>
+        <v>0.145050786354662</v>
       </c>
       <c r="T51">
-        <v>1.644546585541313</v>
+        <v>1.673510843763978</v>
       </c>
       <c r="U51">
         <v>0.0535</v>
@@ -5513,7 +5513,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>5.770556630107436</v>
+        <v>5.655145497505288</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5521,22 +5521,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.09365789317733099</v>
+        <v>0.09382842370730596</v>
       </c>
       <c r="C52">
-        <v>9872.68965895508</v>
+        <v>9666.32012862963</v>
       </c>
       <c r="D52">
-        <v>16494.88965895508</v>
+        <v>16465.91212862963</v>
       </c>
       <c r="E52">
-        <v>3539.5</v>
+        <v>3716.892</v>
       </c>
       <c r="F52">
-        <v>8869.6</v>
+        <v>9046.992</v>
       </c>
       <c r="G52">
         <v>2247.4</v>
@@ -5557,45 +5557,45 @@
         <v>2683.5</v>
       </c>
       <c r="M52">
-        <v>474.5236</v>
+        <v>491.2516656</v>
       </c>
       <c r="N52">
-        <v>2208.9764</v>
+        <v>2192.2483344</v>
       </c>
       <c r="O52">
-        <v>463.885044</v>
+        <v>460.3721502240001</v>
       </c>
       <c r="P52">
-        <v>1745.091356</v>
+        <v>1731.876184176</v>
       </c>
       <c r="Q52">
-        <v>2636.191356</v>
+        <v>2622.976184176</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.145050786354662</v>
+        <v>0.1468386810353183</v>
       </c>
       <c r="T52">
-        <v>1.673510843763978</v>
+        <v>1.703657316607976</v>
       </c>
       <c r="U52">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V52">
         <v>0.21</v>
       </c>
       <c r="W52">
-        <v>0.042265</v>
+        <v>0.042897</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y52">
-        <v>5.655145497505288</v>
+        <v>5.462576898792707</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5603,22 +5603,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.09382842370730596</v>
+        <v>0.09368295423728096</v>
       </c>
       <c r="C53">
-        <v>9666.32012862963</v>
+        <v>9513.640747899533</v>
       </c>
       <c r="D53">
-        <v>16465.91212862963</v>
+        <v>16490.62474789953</v>
       </c>
       <c r="E53">
-        <v>3716.892</v>
+        <v>3894.284</v>
       </c>
       <c r="F53">
-        <v>9046.992</v>
+        <v>9224.384</v>
       </c>
       <c r="G53">
         <v>2247.4</v>
@@ -5639,28 +5639,28 @@
         <v>2683.5</v>
       </c>
       <c r="M53">
-        <v>491.2516656</v>
+        <v>500.8840512</v>
       </c>
       <c r="N53">
-        <v>2192.2483344</v>
+        <v>2182.6159488</v>
       </c>
       <c r="O53">
-        <v>460.3721502240001</v>
+        <v>458.349349248</v>
       </c>
       <c r="P53">
-        <v>1731.876184176</v>
+        <v>1724.266599552</v>
       </c>
       <c r="Q53">
-        <v>2622.976184176</v>
+        <v>2615.366599552</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1468386810353183</v>
+        <v>0.1487010713276686</v>
       </c>
       <c r="T53">
-        <v>1.703657316607976</v>
+        <v>1.735059892487141</v>
       </c>
       <c r="U53">
         <v>0.0543</v>
@@ -5677,7 +5677,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>5.462576898792707</v>
+        <v>5.357527343046693</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5685,22 +5685,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.09368295423728096</v>
+        <v>0.0935374847672559</v>
       </c>
       <c r="C54">
-        <v>9513.640747899533</v>
+        <v>9361.03565780144</v>
       </c>
       <c r="D54">
-        <v>16490.62474789953</v>
+        <v>16515.41165780144</v>
       </c>
       <c r="E54">
-        <v>3894.284</v>
+        <v>4071.676000000001</v>
       </c>
       <c r="F54">
-        <v>9224.384</v>
+        <v>9401.776000000002</v>
       </c>
       <c r="G54">
         <v>2247.4</v>
@@ -5721,28 +5721,28 @@
         <v>2683.5</v>
       </c>
       <c r="M54">
-        <v>500.8840512</v>
+        <v>510.5164368000001</v>
       </c>
       <c r="N54">
-        <v>2182.6159488</v>
+        <v>2172.9835632</v>
       </c>
       <c r="O54">
-        <v>458.349349248</v>
+        <v>456.326548272</v>
       </c>
       <c r="P54">
-        <v>1724.266599552</v>
+        <v>1716.657014928</v>
       </c>
       <c r="Q54">
-        <v>2615.366599552</v>
+        <v>2607.757014928</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1487010713276686</v>
+        <v>0.1506427122707573</v>
       </c>
       <c r="T54">
-        <v>1.735059892487141</v>
+        <v>1.767798748190951</v>
       </c>
       <c r="U54">
         <v>0.0543</v>
@@ -5759,7 +5759,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>5.357527343046693</v>
+        <v>5.256441921479774</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5767,22 +5767,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.0935374847672559</v>
+        <v>0.09339201529723087</v>
       </c>
       <c r="C55">
-        <v>9361.03565780144</v>
+        <v>9208.505193836379</v>
       </c>
       <c r="D55">
-        <v>16515.41165780144</v>
+        <v>16540.27319383638</v>
       </c>
       <c r="E55">
-        <v>4071.676000000001</v>
+        <v>4249.068000000001</v>
       </c>
       <c r="F55">
-        <v>9401.776000000002</v>
+        <v>9579.168000000001</v>
       </c>
       <c r="G55">
         <v>2247.4</v>
@@ -5803,28 +5803,28 @@
         <v>2683.5</v>
       </c>
       <c r="M55">
-        <v>510.5164368000001</v>
+        <v>520.1488224000001</v>
       </c>
       <c r="N55">
-        <v>2172.9835632</v>
+        <v>2163.3511776</v>
       </c>
       <c r="O55">
-        <v>456.326548272</v>
+        <v>454.303747296</v>
       </c>
       <c r="P55">
-        <v>1716.657014928</v>
+        <v>1709.047430304</v>
       </c>
       <c r="Q55">
-        <v>2607.757014928</v>
+        <v>2600.147430304</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1506427122707573</v>
+        <v>0.1526687723852845</v>
       </c>
       <c r="T55">
-        <v>1.767798748190951</v>
+        <v>1.801961032403622</v>
       </c>
       <c r="U55">
         <v>0.0543</v>
@@ -5841,7 +5841,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>5.256441921479774</v>
+        <v>5.159100404415334</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5849,22 +5849,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.09339201529723087</v>
+        <v>0.09324654582720587</v>
       </c>
       <c r="C56">
-        <v>9208.505193836379</v>
+        <v>9056.049693528614</v>
       </c>
       <c r="D56">
-        <v>16540.27319383638</v>
+        <v>16565.20969352861</v>
       </c>
       <c r="E56">
-        <v>4249.068000000001</v>
+        <v>4426.460000000001</v>
       </c>
       <c r="F56">
-        <v>9579.168000000001</v>
+        <v>9756.560000000001</v>
       </c>
       <c r="G56">
         <v>2247.4</v>
@@ -5885,28 +5885,28 @@
         <v>2683.5</v>
       </c>
       <c r="M56">
-        <v>520.1488224000001</v>
+        <v>529.7812080000001</v>
       </c>
       <c r="N56">
-        <v>2163.3511776</v>
+        <v>2153.718792</v>
       </c>
       <c r="O56">
-        <v>454.303747296</v>
+        <v>452.2809463199999</v>
       </c>
       <c r="P56">
-        <v>1709.047430304</v>
+        <v>1701.43784568</v>
       </c>
       <c r="Q56">
-        <v>2600.147430304</v>
+        <v>2592.53784568</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1526687723852845</v>
+        <v>0.1547848796160131</v>
       </c>
       <c r="T56">
-        <v>1.801961032403622</v>
+        <v>1.837641640359079</v>
       </c>
       <c r="U56">
         <v>0.0543</v>
@@ -5923,7 +5923,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>5.159100404415334</v>
+        <v>5.065298578880509</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5931,22 +5931,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.09324654582720587</v>
+        <v>0.09310107635718085</v>
       </c>
       <c r="C57">
-        <v>9056.049693528614</v>
+        <v>8903.669496440933</v>
       </c>
       <c r="D57">
-        <v>16565.20969352861</v>
+        <v>16590.22149644093</v>
       </c>
       <c r="E57">
-        <v>4426.460000000001</v>
+        <v>4603.852000000001</v>
       </c>
       <c r="F57">
-        <v>9756.560000000001</v>
+        <v>9933.952000000001</v>
       </c>
       <c r="G57">
         <v>2247.4</v>
@@ -5967,28 +5967,28 @@
         <v>2683.5</v>
       </c>
       <c r="M57">
-        <v>529.7812080000001</v>
+        <v>539.4135936000001</v>
       </c>
       <c r="N57">
-        <v>2153.718792</v>
+        <v>2144.0864064</v>
       </c>
       <c r="O57">
-        <v>452.2809463199999</v>
+        <v>450.258145344</v>
       </c>
       <c r="P57">
-        <v>1701.43784568</v>
+        <v>1693.828261056</v>
       </c>
       <c r="Q57">
-        <v>2592.53784568</v>
+        <v>2584.928261056</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1547848796160131</v>
+        <v>0.1569971735390474</v>
       </c>
       <c r="T57">
-        <v>1.837641640359079</v>
+        <v>1.874944094130693</v>
       </c>
       <c r="U57">
         <v>0.0543</v>
@@ -6005,7 +6005,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>5.065298578880509</v>
+        <v>4.974846818543357</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6013,22 +6013,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.09310107635718085</v>
+        <v>0.09295560688715583</v>
       </c>
       <c r="C58">
-        <v>8903.669496440933</v>
+        <v>8751.364944190038</v>
       </c>
       <c r="D58">
-        <v>16590.22149644093</v>
+        <v>16615.30894419004</v>
       </c>
       <c r="E58">
-        <v>4603.852000000001</v>
+        <v>4781.244000000001</v>
       </c>
       <c r="F58">
-        <v>9933.952000000001</v>
+        <v>10111.344</v>
       </c>
       <c r="G58">
         <v>2247.4</v>
@@ -6049,28 +6049,28 @@
         <v>2683.5</v>
       </c>
       <c r="M58">
-        <v>539.4135936000001</v>
+        <v>549.0459792</v>
       </c>
       <c r="N58">
-        <v>2144.0864064</v>
+        <v>2134.4540208</v>
       </c>
       <c r="O58">
-        <v>450.258145344</v>
+        <v>448.235344368</v>
       </c>
       <c r="P58">
-        <v>1693.828261056</v>
+        <v>1686.218676432</v>
       </c>
       <c r="Q58">
-        <v>2584.928261056</v>
+        <v>2577.318676432</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1569971735390474</v>
+        <v>0.1593123648538508</v>
       </c>
       <c r="T58">
-        <v>1.874944094130693</v>
+        <v>1.91398154575215</v>
       </c>
       <c r="U58">
         <v>0.0543</v>
@@ -6087,7 +6087,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>4.974846818543357</v>
+        <v>4.887568804182948</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6095,22 +6095,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.09295560688715583</v>
+        <v>0.0928101374171308</v>
       </c>
       <c r="C59">
-        <v>8751.364944190038</v>
+        <v>8599.136380462111</v>
       </c>
       <c r="D59">
-        <v>16615.30894419004</v>
+        <v>16640.47238046211</v>
       </c>
       <c r="E59">
-        <v>4781.244000000001</v>
+        <v>4958.636</v>
       </c>
       <c r="F59">
-        <v>10111.344</v>
+        <v>10288.736</v>
       </c>
       <c r="G59">
         <v>2247.4</v>
@@ -6131,28 +6131,28 @@
         <v>2683.5</v>
       </c>
       <c r="M59">
-        <v>549.0459792</v>
+        <v>558.6783648000001</v>
       </c>
       <c r="N59">
-        <v>2134.4540208</v>
+        <v>2124.8216352</v>
       </c>
       <c r="O59">
-        <v>448.235344368</v>
+        <v>446.212543392</v>
       </c>
       <c r="P59">
-        <v>1686.218676432</v>
+        <v>1678.609091808</v>
       </c>
       <c r="Q59">
-        <v>2577.318676432</v>
+        <v>2569.709091808</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1593123648538508</v>
+        <v>0.161737803374121</v>
       </c>
       <c r="T59">
-        <v>1.91398154575215</v>
+        <v>1.954877923641295</v>
       </c>
       <c r="U59">
         <v>0.0543</v>
@@ -6169,7 +6169,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>4.887568804182948</v>
+        <v>4.803300376524621</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6177,22 +6177,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.09281013741713082</v>
+        <v>0.09266466794710579</v>
       </c>
       <c r="C60">
-        <v>8599.136380462109</v>
+        <v>8446.9841510285</v>
       </c>
       <c r="D60">
-        <v>16640.47238046211</v>
+        <v>16665.7121510285</v>
       </c>
       <c r="E60">
-        <v>4958.635999999999</v>
+        <v>5136.028</v>
       </c>
       <c r="F60">
-        <v>10288.736</v>
+        <v>10466.128</v>
       </c>
       <c r="G60">
         <v>2247.4</v>
@@ -6213,28 +6213,28 @@
         <v>2683.5</v>
       </c>
       <c r="M60">
-        <v>558.6783647999999</v>
+        <v>568.3107504000001</v>
       </c>
       <c r="N60">
-        <v>2124.8216352</v>
+        <v>2115.1892496</v>
       </c>
       <c r="O60">
-        <v>446.212543392</v>
+        <v>444.189742416</v>
       </c>
       <c r="P60">
-        <v>1678.609091808</v>
+        <v>1670.999507184</v>
       </c>
       <c r="Q60">
-        <v>2569.709091808</v>
+        <v>2562.099507184</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.161737803374121</v>
+        <v>0.1642815559685507</v>
       </c>
       <c r="T60">
-        <v>1.954877923641294</v>
+        <v>1.997769246793324</v>
       </c>
       <c r="U60">
         <v>0.0543</v>
@@ -6251,7 +6251,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>4.803300376524622</v>
+        <v>4.721888505736068</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6259,22 +6259,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.09266466794710579</v>
+        <v>0.09251919847708076</v>
       </c>
       <c r="C61">
-        <v>8446.9841510285</v>
+        <v>8294.908603761582</v>
       </c>
       <c r="D61">
-        <v>16665.7121510285</v>
+        <v>16691.02860376158</v>
       </c>
       <c r="E61">
-        <v>5136.028</v>
+        <v>5313.42</v>
       </c>
       <c r="F61">
-        <v>10466.128</v>
+        <v>10643.52</v>
       </c>
       <c r="G61">
         <v>2247.4</v>
@@ -6295,28 +6295,28 @@
         <v>2683.5</v>
       </c>
       <c r="M61">
-        <v>568.3107504000001</v>
+        <v>577.943136</v>
       </c>
       <c r="N61">
-        <v>2115.1892496</v>
+        <v>2105.556864</v>
       </c>
       <c r="O61">
-        <v>444.189742416</v>
+        <v>442.16694144</v>
       </c>
       <c r="P61">
-        <v>1670.999507184</v>
+        <v>1663.38992256</v>
       </c>
       <c r="Q61">
-        <v>2562.099507184</v>
+        <v>2554.48992256</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1642815559685507</v>
+        <v>0.1669524961927019</v>
       </c>
       <c r="T61">
-        <v>1.997769246793324</v>
+        <v>2.042805136102956</v>
       </c>
       <c r="U61">
         <v>0.0543</v>
@@ -6333,7 +6333,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>4.721888505736068</v>
+        <v>4.643190363973801</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6341,22 +6341,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.09251919847708076</v>
+        <v>0.09237372900705575</v>
       </c>
       <c r="C62">
-        <v>8294.908603761582</v>
+        <v>8142.910088650697</v>
       </c>
       <c r="D62">
-        <v>16691.02860376158</v>
+        <v>16716.4220886507</v>
       </c>
       <c r="E62">
-        <v>5313.42</v>
+        <v>5490.812</v>
       </c>
       <c r="F62">
-        <v>10643.52</v>
+        <v>10820.912</v>
       </c>
       <c r="G62">
         <v>2247.4</v>
@@ -6377,28 +6377,28 @@
         <v>2683.5</v>
       </c>
       <c r="M62">
-        <v>577.943136</v>
+        <v>587.5755216</v>
       </c>
       <c r="N62">
-        <v>2105.556864</v>
+        <v>2095.9244784</v>
       </c>
       <c r="O62">
-        <v>442.16694144</v>
+        <v>440.144140464</v>
       </c>
       <c r="P62">
-        <v>1663.38992256</v>
+        <v>1655.780337936</v>
       </c>
       <c r="Q62">
-        <v>2554.48992256</v>
+        <v>2546.880337936</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1669524961927019</v>
+        <v>0.1697604077103993</v>
       </c>
       <c r="T62">
-        <v>2.042805136102956</v>
+        <v>2.090150558197696</v>
       </c>
       <c r="U62">
         <v>0.0543</v>
@@ -6415,7 +6415,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>4.643190363973801</v>
+        <v>4.567072489154558</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.09237372900705575</v>
+        <v>0.09222825953703072</v>
       </c>
       <c r="C63">
-        <v>8142.910088650697</v>
+        <v>7990.988957818328</v>
       </c>
       <c r="D63">
-        <v>16716.4220886507</v>
+        <v>16741.89295781833</v>
       </c>
       <c r="E63">
-        <v>5490.812</v>
+        <v>5668.204</v>
       </c>
       <c r="F63">
-        <v>10820.912</v>
+        <v>10998.304</v>
       </c>
       <c r="G63">
         <v>2247.4</v>
@@ -6459,28 +6459,28 @@
         <v>2683.5</v>
       </c>
       <c r="M63">
-        <v>587.5755216</v>
+        <v>597.2079072</v>
       </c>
       <c r="N63">
-        <v>2095.9244784</v>
+        <v>2086.2920928</v>
       </c>
       <c r="O63">
-        <v>440.144140464</v>
+        <v>438.1213394879999</v>
       </c>
       <c r="P63">
-        <v>1655.780337936</v>
+        <v>1648.170753312</v>
       </c>
       <c r="Q63">
-        <v>2546.880337936</v>
+        <v>2539.270753312</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1697604077103993</v>
+        <v>0.1727161040448177</v>
       </c>
       <c r="T63">
-        <v>2.090150558197696</v>
+        <v>2.139987844613213</v>
       </c>
       <c r="U63">
         <v>0.0543</v>
@@ -6497,7 +6497,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>4.567072489154558</v>
+        <v>4.493410029652065</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6505,22 +6505,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.09222825953703072</v>
+        <v>0.09208279006700569</v>
       </c>
       <c r="C64">
-        <v>7990.988957818328</v>
+        <v>7839.145565536342</v>
       </c>
       <c r="D64">
-        <v>16741.89295781833</v>
+        <v>16767.44156553634</v>
       </c>
       <c r="E64">
-        <v>5668.204</v>
+        <v>5845.596</v>
       </c>
       <c r="F64">
-        <v>10998.304</v>
+        <v>11175.696</v>
       </c>
       <c r="G64">
         <v>2247.4</v>
@@ -6541,28 +6541,28 @@
         <v>2683.5</v>
       </c>
       <c r="M64">
-        <v>597.2079072</v>
+        <v>606.8402928</v>
       </c>
       <c r="N64">
-        <v>2086.2920928</v>
+        <v>2076.6597072</v>
       </c>
       <c r="O64">
-        <v>438.1213394879999</v>
+        <v>436.0985385119999</v>
       </c>
       <c r="P64">
-        <v>1648.170753312</v>
+        <v>1640.561168688</v>
       </c>
       <c r="Q64">
-        <v>2539.270753312</v>
+        <v>2531.661168688</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1727161040448177</v>
+        <v>0.175831567748664</v>
       </c>
       <c r="T64">
-        <v>2.139987844613213</v>
+        <v>2.192519038402541</v>
       </c>
       <c r="U64">
         <v>0.0543</v>
@@ -6579,7 +6579,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>4.493410029652065</v>
+        <v>4.422086060927429</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6587,22 +6587,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.09208279006700569</v>
+        <v>0.09193732059698068</v>
       </c>
       <c r="C65">
-        <v>7839.145565536342</v>
+        <v>7687.380268242427</v>
       </c>
       <c r="D65">
-        <v>16767.44156553634</v>
+        <v>16793.06826824243</v>
       </c>
       <c r="E65">
-        <v>5845.596</v>
+        <v>6022.988000000001</v>
       </c>
       <c r="F65">
-        <v>11175.696</v>
+        <v>11353.088</v>
       </c>
       <c r="G65">
         <v>2247.4</v>
@@ -6623,28 +6623,28 @@
         <v>2683.5</v>
       </c>
       <c r="M65">
-        <v>606.8402928</v>
+        <v>616.4726784000001</v>
       </c>
       <c r="N65">
-        <v>2076.6597072</v>
+        <v>2067.0273216</v>
       </c>
       <c r="O65">
-        <v>436.0985385119999</v>
+        <v>434.075737536</v>
       </c>
       <c r="P65">
-        <v>1640.561168688</v>
+        <v>1632.951584064</v>
       </c>
       <c r="Q65">
-        <v>2531.661168688</v>
+        <v>2524.051584064</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.175831567748664</v>
+        <v>0.1791201127693908</v>
       </c>
       <c r="T65">
-        <v>2.192519038402541</v>
+        <v>2.247968631846833</v>
       </c>
       <c r="U65">
         <v>0.0543</v>
@@ -6661,7 +6661,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>4.422086060927429</v>
+        <v>4.352990966225438</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6669,22 +6669,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.09193732059698068</v>
+        <v>0.09179185112695566</v>
       </c>
       <c r="C66">
-        <v>7687.380268242427</v>
+        <v>7535.693424556672</v>
       </c>
       <c r="D66">
-        <v>16793.06826824243</v>
+        <v>16818.77342455667</v>
       </c>
       <c r="E66">
-        <v>6022.988000000001</v>
+        <v>6200.380000000001</v>
       </c>
       <c r="F66">
-        <v>11353.088</v>
+        <v>11530.48</v>
       </c>
       <c r="G66">
         <v>2247.4</v>
@@ -6705,28 +6705,28 @@
         <v>2683.5</v>
       </c>
       <c r="M66">
-        <v>616.4726784000001</v>
+        <v>626.1050640000001</v>
       </c>
       <c r="N66">
-        <v>2067.0273216</v>
+        <v>2057.394936</v>
       </c>
       <c r="O66">
-        <v>434.075737536</v>
+        <v>432.0529365599999</v>
       </c>
       <c r="P66">
-        <v>1632.951584064</v>
+        <v>1625.34199944</v>
       </c>
       <c r="Q66">
-        <v>2524.051584064</v>
+        <v>2516.44199944</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1791201127693908</v>
+        <v>0.1825965746484447</v>
       </c>
       <c r="T66">
-        <v>2.247968631846833</v>
+        <v>2.306586773487941</v>
       </c>
       <c r="U66">
         <v>0.0543</v>
@@ -6743,7 +6743,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>4.352990966225438</v>
+        <v>4.286021874437354</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6751,22 +6751,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.09179185112695566</v>
+        <v>0.09216778165693063</v>
       </c>
       <c r="C67">
-        <v>7535.693424556672</v>
+        <v>7292.03314495025</v>
       </c>
       <c r="D67">
-        <v>16818.77342455667</v>
+        <v>16752.50514495025</v>
       </c>
       <c r="E67">
-        <v>6200.380000000001</v>
+        <v>6377.772000000001</v>
       </c>
       <c r="F67">
-        <v>11530.48</v>
+        <v>11707.872</v>
       </c>
       <c r="G67">
         <v>2247.4</v>
@@ -6787,45 +6787,45 @@
         <v>2683.5</v>
       </c>
       <c r="M67">
-        <v>626.1050640000001</v>
+        <v>647.4453216000001</v>
       </c>
       <c r="N67">
-        <v>2057.394936</v>
+        <v>2036.0546784</v>
       </c>
       <c r="O67">
-        <v>432.0529365599999</v>
+        <v>427.5714824639999</v>
       </c>
       <c r="P67">
-        <v>1625.34199944</v>
+        <v>1608.483195936</v>
       </c>
       <c r="Q67">
-        <v>2516.44199944</v>
+        <v>2499.583195936</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1825965746484447</v>
+        <v>0.1862775342850901</v>
       </c>
       <c r="T67">
-        <v>2.306586773487941</v>
+        <v>2.368653041107937</v>
       </c>
       <c r="U67">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V67">
         <v>0.21</v>
       </c>
       <c r="W67">
-        <v>0.042897</v>
+        <v>0.043687</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y67">
-        <v>4.286021874437354</v>
+        <v>4.144751549626457</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6833,22 +6833,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.09216778165693063</v>
+        <v>0.0920302121869056</v>
       </c>
       <c r="C68">
-        <v>7292.03314495025</v>
+        <v>7138.830943462121</v>
       </c>
       <c r="D68">
-        <v>16752.50514495025</v>
+        <v>16776.69494346212</v>
       </c>
       <c r="E68">
-        <v>6377.772000000001</v>
+        <v>6555.164000000001</v>
       </c>
       <c r="F68">
-        <v>11707.872</v>
+        <v>11885.264</v>
       </c>
       <c r="G68">
         <v>2247.4</v>
@@ -6869,28 +6869,28 @@
         <v>2683.5</v>
       </c>
       <c r="M68">
-        <v>647.4453216000001</v>
+        <v>657.2550992000001</v>
       </c>
       <c r="N68">
-        <v>2036.0546784</v>
+        <v>2026.2449008</v>
       </c>
       <c r="O68">
-        <v>427.5714824639999</v>
+        <v>425.5114291679999</v>
       </c>
       <c r="P68">
-        <v>1608.483195936</v>
+        <v>1600.733471632</v>
       </c>
       <c r="Q68">
-        <v>2499.583195936</v>
+        <v>2491.833471632</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1862775342850901</v>
+        <v>0.1901815823845625</v>
       </c>
       <c r="T68">
-        <v>2.368653041107937</v>
+        <v>2.434480900704903</v>
       </c>
       <c r="U68">
         <v>0.0553</v>
@@ -6907,7 +6907,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>4.144751549626457</v>
+        <v>4.082889586199196</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6915,22 +6915,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.0920302121869056</v>
+        <v>0.09189264271688058</v>
       </c>
       <c r="C69">
-        <v>7138.830943462121</v>
+        <v>6985.698700764215</v>
       </c>
       <c r="D69">
-        <v>16776.69494346212</v>
+        <v>16800.95470076421</v>
       </c>
       <c r="E69">
-        <v>6555.164000000001</v>
+        <v>6732.556</v>
       </c>
       <c r="F69">
-        <v>11885.264</v>
+        <v>12062.656</v>
       </c>
       <c r="G69">
         <v>2247.4</v>
@@ -6951,28 +6951,28 @@
         <v>2683.5</v>
       </c>
       <c r="M69">
-        <v>657.2550992000001</v>
+        <v>667.0648768000001</v>
       </c>
       <c r="N69">
-        <v>2026.2449008</v>
+        <v>2016.4351232</v>
       </c>
       <c r="O69">
-        <v>425.5114291679999</v>
+        <v>423.451375872</v>
       </c>
       <c r="P69">
-        <v>1600.733471632</v>
+        <v>1592.983747328</v>
       </c>
       <c r="Q69">
-        <v>2491.833471632</v>
+        <v>2484.083747328</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1901815823845625</v>
+        <v>0.1943296334902518</v>
       </c>
       <c r="T69">
-        <v>2.434480900704903</v>
+        <v>2.504423001526679</v>
       </c>
       <c r="U69">
         <v>0.0553</v>
@@ -6989,7 +6989,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>4.082889586199196</v>
+        <v>4.022847092284502</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6997,22 +6997,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.09189264271688058</v>
+        <v>0.09175507324685556</v>
       </c>
       <c r="C70">
-        <v>6985.698700764215</v>
+        <v>6832.636720785469</v>
       </c>
       <c r="D70">
-        <v>16800.95470076421</v>
+        <v>16825.28472078547</v>
       </c>
       <c r="E70">
-        <v>6732.556</v>
+        <v>6909.948</v>
       </c>
       <c r="F70">
-        <v>12062.656</v>
+        <v>12240.048</v>
       </c>
       <c r="G70">
         <v>2247.4</v>
@@ -7033,28 +7033,28 @@
         <v>2683.5</v>
       </c>
       <c r="M70">
-        <v>667.0648768000001</v>
+        <v>676.8746544000001</v>
       </c>
       <c r="N70">
-        <v>2016.4351232</v>
+        <v>2006.6253456</v>
       </c>
       <c r="O70">
-        <v>423.451375872</v>
+        <v>421.391322576</v>
       </c>
       <c r="P70">
-        <v>1592.983747328</v>
+        <v>1585.234023024</v>
       </c>
       <c r="Q70">
-        <v>2484.083747328</v>
+        <v>2476.334023024</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1943296334902518</v>
+        <v>0.1987453007963083</v>
       </c>
       <c r="T70">
-        <v>2.504423001526679</v>
+        <v>2.57887749594986</v>
       </c>
       <c r="U70">
         <v>0.0553</v>
@@ -7071,7 +7071,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>4.022847092284502</v>
+        <v>3.964544960512263</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7079,22 +7079,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.09175507324685556</v>
+        <v>0.09161750377683053</v>
       </c>
       <c r="C71">
-        <v>6832.636720785469</v>
+        <v>6679.645309217885</v>
       </c>
       <c r="D71">
-        <v>16825.28472078547</v>
+        <v>16849.68530921789</v>
       </c>
       <c r="E71">
-        <v>6909.948</v>
+        <v>7087.340000000002</v>
       </c>
       <c r="F71">
-        <v>12240.048</v>
+        <v>12417.44</v>
       </c>
       <c r="G71">
         <v>2247.4</v>
@@ -7115,28 +7115,28 @@
         <v>2683.5</v>
       </c>
       <c r="M71">
-        <v>676.8746544000001</v>
+        <v>686.6844320000001</v>
       </c>
       <c r="N71">
-        <v>2006.6253456</v>
+        <v>1996.815568</v>
       </c>
       <c r="O71">
-        <v>421.391322576</v>
+        <v>419.33126928</v>
       </c>
       <c r="P71">
-        <v>1585.234023024</v>
+        <v>1577.48429872</v>
       </c>
       <c r="Q71">
-        <v>2476.334023024</v>
+        <v>2468.58429872</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1987453007963083</v>
+        <v>0.2034553459227685</v>
       </c>
       <c r="T71">
-        <v>2.57887749594986</v>
+        <v>2.658295623334587</v>
       </c>
       <c r="U71">
         <v>0.0553</v>
@@ -7153,7 +7153,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>3.964544960512263</v>
+        <v>3.907908603933516</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7161,22 +7161,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.09161750377683053</v>
+        <v>0.09147993430680552</v>
       </c>
       <c r="C72">
-        <v>6679.645309217885</v>
+        <v>6526.724773529357</v>
       </c>
       <c r="D72">
-        <v>16849.68530921789</v>
+        <v>16874.15677352936</v>
       </c>
       <c r="E72">
-        <v>7087.340000000002</v>
+        <v>7264.732000000002</v>
       </c>
       <c r="F72">
-        <v>12417.44</v>
+        <v>12594.832</v>
       </c>
       <c r="G72">
         <v>2247.4</v>
@@ -7197,28 +7197,28 @@
         <v>2683.5</v>
       </c>
       <c r="M72">
-        <v>686.6844320000001</v>
+        <v>696.4942096000001</v>
       </c>
       <c r="N72">
-        <v>1996.815568</v>
+        <v>1987.0057904</v>
       </c>
       <c r="O72">
-        <v>419.33126928</v>
+        <v>417.271215984</v>
       </c>
       <c r="P72">
-        <v>1577.48429872</v>
+        <v>1569.734574416</v>
       </c>
       <c r="Q72">
-        <v>2468.58429872</v>
+        <v>2460.834574416</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2034553459227685</v>
+        <v>0.2084902217476053</v>
       </c>
       <c r="T72">
-        <v>2.658295623334587</v>
+        <v>2.743190862952743</v>
       </c>
       <c r="U72">
         <v>0.0553</v>
@@ -7235,7 +7235,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>3.907908603933516</v>
+        <v>3.852867637680932</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7243,22 +7243,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.09147993430680552</v>
+        <v>0.09134236483678049</v>
       </c>
       <c r="C73">
-        <v>6526.724773529359</v>
+        <v>6373.875422976553</v>
       </c>
       <c r="D73">
-        <v>16874.15677352936</v>
+        <v>16898.69942297655</v>
       </c>
       <c r="E73">
-        <v>7264.732</v>
+        <v>7442.124</v>
       </c>
       <c r="F73">
-        <v>12594.832</v>
+        <v>12772.224</v>
       </c>
       <c r="G73">
         <v>2247.4</v>
@@ -7279,28 +7279,28 @@
         <v>2683.5</v>
       </c>
       <c r="M73">
-        <v>696.4942096000001</v>
+        <v>706.3039872000001</v>
       </c>
       <c r="N73">
-        <v>1987.0057904</v>
+        <v>1977.1960128</v>
       </c>
       <c r="O73">
-        <v>417.271215984</v>
+        <v>415.211162688</v>
       </c>
       <c r="P73">
-        <v>1569.734574416</v>
+        <v>1561.984850112</v>
       </c>
       <c r="Q73">
-        <v>2460.834574416</v>
+        <v>2453.084850112</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2084902217476052</v>
+        <v>0.2138847315599303</v>
       </c>
       <c r="T73">
-        <v>2.743190862952742</v>
+        <v>2.834150048257909</v>
       </c>
       <c r="U73">
         <v>0.0553</v>
@@ -7317,7 +7317,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>3.852867637680932</v>
+        <v>3.799355587157586</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7325,22 +7325,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.09134236483678049</v>
+        <v>0.09120479536675546</v>
       </c>
       <c r="C74">
-        <v>6373.875422976553</v>
+        <v>6221.097568617954</v>
       </c>
       <c r="D74">
-        <v>16898.69942297655</v>
+        <v>16923.31356861795</v>
       </c>
       <c r="E74">
-        <v>7442.124</v>
+        <v>7619.516</v>
       </c>
       <c r="F74">
-        <v>12772.224</v>
+        <v>12949.616</v>
       </c>
       <c r="G74">
         <v>2247.4</v>
@@ -7361,28 +7361,28 @@
         <v>2683.5</v>
       </c>
       <c r="M74">
-        <v>706.3039872000001</v>
+        <v>716.1137648</v>
       </c>
       <c r="N74">
-        <v>1977.1960128</v>
+        <v>1967.3862352</v>
       </c>
       <c r="O74">
-        <v>415.211162688</v>
+        <v>413.151109392</v>
       </c>
       <c r="P74">
-        <v>1561.984850112</v>
+        <v>1554.235125808</v>
       </c>
       <c r="Q74">
-        <v>2453.084850112</v>
+        <v>2445.335125808</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2138847315599303</v>
+        <v>0.2196788346916869</v>
       </c>
       <c r="T74">
-        <v>2.834150048257909</v>
+        <v>2.931846950993088</v>
       </c>
       <c r="U74">
         <v>0.0553</v>
@@ -7399,7 +7399,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>3.799355587157586</v>
+        <v>3.747309620210222</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7407,22 +7407,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.09120479536675546</v>
+        <v>0.09106722589673044</v>
       </c>
       <c r="C75">
-        <v>6221.097568617954</v>
+        <v>6068.391523327011</v>
       </c>
       <c r="D75">
-        <v>16923.31356861795</v>
+        <v>16947.99952332701</v>
       </c>
       <c r="E75">
-        <v>7619.516</v>
+        <v>7796.907999999999</v>
       </c>
       <c r="F75">
-        <v>12949.616</v>
+        <v>13127.008</v>
       </c>
       <c r="G75">
         <v>2247.4</v>
@@ -7443,28 +7443,28 @@
         <v>2683.5</v>
       </c>
       <c r="M75">
-        <v>716.1137648</v>
+        <v>725.9235424</v>
       </c>
       <c r="N75">
-        <v>1967.3862352</v>
+        <v>1957.5764576</v>
       </c>
       <c r="O75">
-        <v>413.151109392</v>
+        <v>411.091056096</v>
       </c>
       <c r="P75">
-        <v>1554.235125808</v>
+        <v>1546.485401504</v>
       </c>
       <c r="Q75">
-        <v>2445.335125808</v>
+        <v>2437.585401504</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2196788346916869</v>
+        <v>0.2259186380643479</v>
       </c>
       <c r="T75">
-        <v>2.931846950993088</v>
+        <v>3.037059000092513</v>
       </c>
       <c r="U75">
         <v>0.0553</v>
@@ -7481,7 +7481,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>3.747309620210222</v>
+        <v>3.696670301018192</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7489,22 +7489,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.09106722589673044</v>
+        <v>0.09092965642670542</v>
       </c>
       <c r="C76">
-        <v>6068.391523327011</v>
+        <v>5915.757601805384</v>
       </c>
       <c r="D76">
-        <v>16947.99952332701</v>
+        <v>16972.75760180538</v>
       </c>
       <c r="E76">
-        <v>7796.907999999999</v>
+        <v>7974.300000000001</v>
       </c>
       <c r="F76">
-        <v>13127.008</v>
+        <v>13304.4</v>
       </c>
       <c r="G76">
         <v>2247.4</v>
@@ -7525,28 +7525,28 @@
         <v>2683.5</v>
       </c>
       <c r="M76">
-        <v>725.9235424</v>
+        <v>735.7333200000002</v>
       </c>
       <c r="N76">
-        <v>1957.5764576</v>
+        <v>1947.76668</v>
       </c>
       <c r="O76">
-        <v>411.091056096</v>
+        <v>409.0310028</v>
       </c>
       <c r="P76">
-        <v>1546.485401504</v>
+        <v>1538.7356772</v>
       </c>
       <c r="Q76">
-        <v>2437.585401504</v>
+        <v>2429.8356772</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2259186380643479</v>
+        <v>0.2326576257068217</v>
       </c>
       <c r="T76">
-        <v>3.037059000092513</v>
+        <v>3.150688013119891</v>
       </c>
       <c r="U76">
         <v>0.0553</v>
@@ -7563,7 +7563,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>3.696670301018192</v>
+        <v>3.647381363671281</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7571,22 +7571,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.09092965642670542</v>
+        <v>0.0907920869566804</v>
       </c>
       <c r="C77">
-        <v>5915.757601805384</v>
+        <v>5763.196120596323</v>
       </c>
       <c r="D77">
-        <v>16972.75760180538</v>
+        <v>16997.58812059632</v>
       </c>
       <c r="E77">
-        <v>7974.300000000001</v>
+        <v>8151.692000000001</v>
       </c>
       <c r="F77">
-        <v>13304.4</v>
+        <v>13481.792</v>
       </c>
       <c r="G77">
         <v>2247.4</v>
@@ -7607,28 +7607,28 @@
         <v>2683.5</v>
       </c>
       <c r="M77">
-        <v>735.7333200000002</v>
+        <v>745.5430976000001</v>
       </c>
       <c r="N77">
-        <v>1947.76668</v>
+        <v>1937.9569024</v>
       </c>
       <c r="O77">
-        <v>409.0310028</v>
+        <v>406.9709495039999</v>
       </c>
       <c r="P77">
-        <v>1538.7356772</v>
+        <v>1530.985952896</v>
       </c>
       <c r="Q77">
-        <v>2429.8356772</v>
+        <v>2422.085952896</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2326576257068217</v>
+        <v>0.239958195652835</v>
       </c>
       <c r="T77">
-        <v>3.150688013119891</v>
+        <v>3.273786110566217</v>
       </c>
       <c r="U77">
         <v>0.0553</v>
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>3.647381363671281</v>
+        <v>3.599389503622975</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7653,22 +7653,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.0907920869566804</v>
+        <v>0.09065451748665537</v>
       </c>
       <c r="C78">
-        <v>5763.196120596323</v>
+        <v>5610.707398098155</v>
       </c>
       <c r="D78">
-        <v>16997.58812059632</v>
+        <v>17022.49139809815</v>
       </c>
       <c r="E78">
-        <v>8151.692000000001</v>
+        <v>8329.084000000001</v>
       </c>
       <c r="F78">
-        <v>13481.792</v>
+        <v>13659.184</v>
       </c>
       <c r="G78">
         <v>2247.4</v>
@@ -7689,28 +7689,28 @@
         <v>2683.5</v>
       </c>
       <c r="M78">
-        <v>745.5430976000001</v>
+        <v>755.3528752000001</v>
       </c>
       <c r="N78">
-        <v>1937.9569024</v>
+        <v>1928.1471248</v>
       </c>
       <c r="O78">
-        <v>406.9709495039999</v>
+        <v>404.9108962079999</v>
       </c>
       <c r="P78">
-        <v>1530.985952896</v>
+        <v>1523.236228592</v>
       </c>
       <c r="Q78">
-        <v>2422.085952896</v>
+        <v>2414.336228592</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.239958195652835</v>
+        <v>0.2478935977680669</v>
       </c>
       <c r="T78">
-        <v>3.273786110566217</v>
+        <v>3.40758839039918</v>
       </c>
       <c r="U78">
         <v>0.0553</v>
@@ -7727,7 +7727,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>3.599389503622975</v>
+        <v>3.552644185394106</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7735,22 +7735,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.09065451748665537</v>
+        <v>0.09051694801663035</v>
       </c>
       <c r="C79">
-        <v>5610.707398098155</v>
+        <v>5458.291754577895</v>
       </c>
       <c r="D79">
-        <v>17022.49139809815</v>
+        <v>17047.46775457789</v>
       </c>
       <c r="E79">
-        <v>8329.084000000001</v>
+        <v>8506.476000000001</v>
       </c>
       <c r="F79">
-        <v>13659.184</v>
+        <v>13836.576</v>
       </c>
       <c r="G79">
         <v>2247.4</v>
@@ -7771,28 +7771,28 @@
         <v>2683.5</v>
       </c>
       <c r="M79">
-        <v>755.3528752000001</v>
+        <v>765.1626528</v>
       </c>
       <c r="N79">
-        <v>1928.1471248</v>
+        <v>1918.3373472</v>
       </c>
       <c r="O79">
-        <v>404.9108962079999</v>
+        <v>402.850842912</v>
       </c>
       <c r="P79">
-        <v>1523.236228592</v>
+        <v>1515.486504288</v>
       </c>
       <c r="Q79">
-        <v>2414.336228592</v>
+        <v>2406.586504288</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2478935977680669</v>
+        <v>0.2565504000755925</v>
       </c>
       <c r="T79">
-        <v>3.40758839039918</v>
+        <v>3.553554513853322</v>
       </c>
       <c r="U79">
         <v>0.0553</v>
@@ -7809,7 +7809,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>3.552644185394106</v>
+        <v>3.50709746506854</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7817,22 +7817,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.09051694801663035</v>
+        <v>0.09037937854660534</v>
       </c>
       <c r="C80">
-        <v>5458.291754577895</v>
+        <v>5305.949512184969</v>
       </c>
       <c r="D80">
-        <v>17047.46775457789</v>
+        <v>17072.51751218497</v>
       </c>
       <c r="E80">
-        <v>8506.476000000001</v>
+        <v>8683.868</v>
       </c>
       <c r="F80">
-        <v>13836.576</v>
+        <v>14013.968</v>
       </c>
       <c r="G80">
         <v>2247.4</v>
@@ -7853,28 +7853,28 @@
         <v>2683.5</v>
       </c>
       <c r="M80">
-        <v>765.1626528</v>
+        <v>774.9724304000001</v>
       </c>
       <c r="N80">
-        <v>1918.3373472</v>
+        <v>1908.5275696</v>
       </c>
       <c r="O80">
-        <v>402.850842912</v>
+        <v>400.790789616</v>
       </c>
       <c r="P80">
-        <v>1515.486504288</v>
+        <v>1507.736779984</v>
       </c>
       <c r="Q80">
-        <v>2406.586504288</v>
+        <v>2398.836779984</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2565504000755925</v>
+        <v>0.2660316597457397</v>
       </c>
       <c r="T80">
-        <v>3.553554513853322</v>
+        <v>3.713422172874525</v>
       </c>
       <c r="U80">
         <v>0.0553</v>
@@ -7891,7 +7891,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>3.50709746506854</v>
+        <v>3.462703826270204</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7899,22 +7899,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.09037937854660534</v>
+        <v>0.09024180907658032</v>
       </c>
       <c r="C81">
-        <v>5305.949512184969</v>
+        <v>5153.680994965085</v>
       </c>
       <c r="D81">
-        <v>17072.51751218497</v>
+        <v>17097.64099496508</v>
       </c>
       <c r="E81">
-        <v>8683.868</v>
+        <v>8861.26</v>
       </c>
       <c r="F81">
-        <v>14013.968</v>
+        <v>14191.36</v>
       </c>
       <c r="G81">
         <v>2247.4</v>
@@ -7935,28 +7935,28 @@
         <v>2683.5</v>
       </c>
       <c r="M81">
-        <v>774.9724304000001</v>
+        <v>784.7822080000001</v>
       </c>
       <c r="N81">
-        <v>1908.5275696</v>
+        <v>1898.717792</v>
       </c>
       <c r="O81">
-        <v>400.790789616</v>
+        <v>398.7307363199999</v>
       </c>
       <c r="P81">
-        <v>1507.736779984</v>
+        <v>1499.98705568</v>
       </c>
       <c r="Q81">
-        <v>2398.836779984</v>
+        <v>2391.08705568</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2660316597457397</v>
+        <v>0.2764610453829016</v>
       </c>
       <c r="T81">
-        <v>3.713422172874525</v>
+        <v>3.889276597797848</v>
       </c>
       <c r="U81">
         <v>0.0553</v>
@@ -7973,7 +7973,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>3.462703826270204</v>
+        <v>3.419420028441827</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7981,22 +7981,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.09024180907658032</v>
+        <v>0.09010423960655528</v>
       </c>
       <c r="C82">
-        <v>5153.680994965085</v>
+        <v>5001.48652887418</v>
       </c>
       <c r="D82">
-        <v>17097.64099496508</v>
+        <v>17122.83852887418</v>
       </c>
       <c r="E82">
-        <v>8861.26</v>
+        <v>9038.652000000002</v>
       </c>
       <c r="F82">
-        <v>14191.36</v>
+        <v>14368.752</v>
       </c>
       <c r="G82">
         <v>2247.4</v>
@@ -8017,28 +8017,28 @@
         <v>2683.5</v>
       </c>
       <c r="M82">
-        <v>784.7822080000001</v>
+        <v>794.5919856000002</v>
       </c>
       <c r="N82">
-        <v>1898.717792</v>
+        <v>1888.9080144</v>
       </c>
       <c r="O82">
-        <v>398.7307363199999</v>
+        <v>396.670683024</v>
       </c>
       <c r="P82">
-        <v>1499.98705568</v>
+        <v>1492.237331376</v>
       </c>
       <c r="Q82">
-        <v>2391.08705568</v>
+        <v>2383.337331376</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2764610453829016</v>
+        <v>0.2879882610871332</v>
       </c>
       <c r="T82">
-        <v>3.889276597797848</v>
+        <v>4.083642014818364</v>
       </c>
       <c r="U82">
         <v>0.0553</v>
@@ -8055,7 +8055,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>3.419420028441827</v>
+        <v>3.377204966362298</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8063,22 +8063,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.09010423960655528</v>
+        <v>0.08996667013653027</v>
       </c>
       <c r="C83">
-        <v>5001.48652887418</v>
+        <v>4849.366441792527</v>
       </c>
       <c r="D83">
-        <v>17122.83852887418</v>
+        <v>17148.11044179253</v>
       </c>
       <c r="E83">
-        <v>9038.652000000002</v>
+        <v>9216.044000000002</v>
       </c>
       <c r="F83">
-        <v>14368.752</v>
+        <v>14546.144</v>
       </c>
       <c r="G83">
         <v>2247.4</v>
@@ -8099,28 +8099,28 @@
         <v>2683.5</v>
       </c>
       <c r="M83">
-        <v>794.5919856000002</v>
+        <v>804.4017632000001</v>
       </c>
       <c r="N83">
-        <v>1888.9080144</v>
+        <v>1879.0982368</v>
       </c>
       <c r="O83">
-        <v>396.670683024</v>
+        <v>394.610629728</v>
       </c>
       <c r="P83">
-        <v>1492.237331376</v>
+        <v>1484.487607072</v>
       </c>
       <c r="Q83">
-        <v>2383.337331376</v>
+        <v>2375.587607072</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2879882610871332</v>
+        <v>0.3007962785362793</v>
       </c>
       <c r="T83">
-        <v>4.083642014818364</v>
+        <v>4.299603589285602</v>
       </c>
       <c r="U83">
         <v>0.0553</v>
@@ -8137,7 +8137,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>3.377204966362298</v>
+        <v>3.336019539943246</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8145,22 +8145,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.08996667013653027</v>
+        <v>0.08982910066650525</v>
       </c>
       <c r="C84">
-        <v>4849.366441792527</v>
+        <v>4697.321063538964</v>
       </c>
       <c r="D84">
-        <v>17148.11044179253</v>
+        <v>17173.45706353896</v>
       </c>
       <c r="E84">
-        <v>9216.044000000002</v>
+        <v>9393.436000000002</v>
       </c>
       <c r="F84">
-        <v>14546.144</v>
+        <v>14723.536</v>
       </c>
       <c r="G84">
         <v>2247.4</v>
@@ -8181,28 +8181,28 @@
         <v>2683.5</v>
       </c>
       <c r="M84">
-        <v>804.4017632000001</v>
+        <v>814.2115408000001</v>
       </c>
       <c r="N84">
-        <v>1879.0982368</v>
+        <v>1869.2884592</v>
       </c>
       <c r="O84">
-        <v>394.610629728</v>
+        <v>392.550576432</v>
       </c>
       <c r="P84">
-        <v>1484.487607072</v>
+        <v>1476.737882768</v>
       </c>
       <c r="Q84">
-        <v>2375.587607072</v>
+        <v>2367.837882768</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3007962785362793</v>
+        <v>0.315111121567678</v>
       </c>
       <c r="T84">
-        <v>4.299603589285602</v>
+        <v>4.540972407807811</v>
       </c>
       <c r="U84">
         <v>0.0553</v>
@@ -8219,7 +8219,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>3.336019539943246</v>
+        <v>3.295826533437906</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8227,22 +8227,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.08982910066650525</v>
+        <v>0.08969153119648023</v>
       </c>
       <c r="C85">
-        <v>4697.321063538964</v>
+        <v>4545.350725885239</v>
       </c>
       <c r="D85">
-        <v>17173.45706353896</v>
+        <v>17198.87872588524</v>
       </c>
       <c r="E85">
-        <v>9393.436000000002</v>
+        <v>9570.828000000001</v>
       </c>
       <c r="F85">
-        <v>14723.536</v>
+        <v>14900.928</v>
       </c>
       <c r="G85">
         <v>2247.4</v>
@@ -8263,28 +8263,28 @@
         <v>2683.5</v>
       </c>
       <c r="M85">
-        <v>814.2115408000001</v>
+        <v>824.0213184000002</v>
       </c>
       <c r="N85">
-        <v>1869.2884592</v>
+        <v>1859.4786816</v>
       </c>
       <c r="O85">
-        <v>392.550576432</v>
+        <v>390.490523136</v>
       </c>
       <c r="P85">
-        <v>1476.737882768</v>
+        <v>1468.988158464</v>
       </c>
       <c r="Q85">
-        <v>2367.837882768</v>
+        <v>2360.088158464</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.315111121567678</v>
+        <v>0.3312153199780015</v>
       </c>
       <c r="T85">
-        <v>4.540972407807811</v>
+        <v>4.812512328645296</v>
       </c>
       <c r="U85">
         <v>0.0553</v>
@@ -8301,7 +8301,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>3.295826533437906</v>
+        <v>3.25659050327793</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8309,22 +8309,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.08969153119648023</v>
+        <v>0.0895539617264552</v>
       </c>
       <c r="C86">
-        <v>4545.350725885241</v>
+        <v>4393.455762570484</v>
       </c>
       <c r="D86">
-        <v>17198.87872588524</v>
+        <v>17224.37576257048</v>
       </c>
       <c r="E86">
-        <v>9570.828</v>
+        <v>9748.219999999999</v>
       </c>
       <c r="F86">
-        <v>14900.928</v>
+        <v>15078.32</v>
       </c>
       <c r="G86">
         <v>2247.4</v>
@@ -8345,28 +8345,28 @@
         <v>2683.5</v>
       </c>
       <c r="M86">
-        <v>824.0213184</v>
+        <v>833.831096</v>
       </c>
       <c r="N86">
-        <v>1859.4786816</v>
+        <v>1849.668904</v>
       </c>
       <c r="O86">
-        <v>390.490523136</v>
+        <v>388.43046984</v>
       </c>
       <c r="P86">
-        <v>1468.988158464</v>
+        <v>1461.23843416</v>
       </c>
       <c r="Q86">
-        <v>2360.088158464</v>
+        <v>2352.33843416</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3312153199780014</v>
+        <v>0.3494667448430346</v>
       </c>
       <c r="T86">
-        <v>4.812512328645292</v>
+        <v>5.120257572261108</v>
       </c>
       <c r="U86">
         <v>0.0553</v>
@@ -8383,7 +8383,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>3.256590503277931</v>
+        <v>3.218277673827602</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8391,22 +8391,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.0895539617264552</v>
+        <v>0.08941639225643019</v>
       </c>
       <c r="C87">
-        <v>4393.455762570484</v>
+        <v>4241.636509315798</v>
       </c>
       <c r="D87">
-        <v>17224.37576257048</v>
+        <v>17249.9485093158</v>
       </c>
       <c r="E87">
-        <v>9748.219999999999</v>
+        <v>9925.611999999999</v>
       </c>
       <c r="F87">
-        <v>15078.32</v>
+        <v>15255.712</v>
       </c>
       <c r="G87">
         <v>2247.4</v>
@@ -8427,28 +8427,28 @@
         <v>2683.5</v>
       </c>
       <c r="M87">
-        <v>833.831096</v>
+        <v>843.6408736</v>
       </c>
       <c r="N87">
-        <v>1849.668904</v>
+        <v>1839.8591264</v>
       </c>
       <c r="O87">
-        <v>388.43046984</v>
+        <v>386.370416544</v>
       </c>
       <c r="P87">
-        <v>1461.23843416</v>
+        <v>1453.488709856</v>
       </c>
       <c r="Q87">
-        <v>2352.33843416</v>
+        <v>2344.588709856</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3494667448430346</v>
+        <v>0.3703255161173584</v>
       </c>
       <c r="T87">
-        <v>5.120257572261108</v>
+        <v>5.471966422107754</v>
       </c>
       <c r="U87">
         <v>0.0553</v>
@@ -8465,7 +8465,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>3.218277673827602</v>
+        <v>3.180855840411002</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8473,22 +8473,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.08941639225643019</v>
+        <v>0.08927882278640517</v>
       </c>
       <c r="C88">
-        <v>4241.636509315798</v>
+        <v>4089.893303839037</v>
       </c>
       <c r="D88">
-        <v>17249.9485093158</v>
+        <v>17275.59730383904</v>
       </c>
       <c r="E88">
-        <v>9925.611999999999</v>
+        <v>10103.004</v>
       </c>
       <c r="F88">
-        <v>15255.712</v>
+        <v>15433.104</v>
       </c>
       <c r="G88">
         <v>2247.4</v>
@@ -8509,28 +8509,28 @@
         <v>2683.5</v>
       </c>
       <c r="M88">
-        <v>843.6408736</v>
+        <v>853.4506512</v>
       </c>
       <c r="N88">
-        <v>1839.8591264</v>
+        <v>1830.0493488</v>
       </c>
       <c r="O88">
-        <v>386.370416544</v>
+        <v>384.310363248</v>
       </c>
       <c r="P88">
-        <v>1453.488709856</v>
+        <v>1445.738985552</v>
       </c>
       <c r="Q88">
-        <v>2344.588709856</v>
+        <v>2336.838985552</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3703255161173584</v>
+        <v>0.3943933291261935</v>
       </c>
       <c r="T88">
-        <v>5.471966422107754</v>
+        <v>5.877784325776961</v>
       </c>
       <c r="U88">
         <v>0.0553</v>
@@ -8547,7 +8547,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>3.180855840411002</v>
+        <v>3.144294279026968</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8555,22 +8555,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.08927882278640517</v>
+        <v>0.08914125331638015</v>
       </c>
       <c r="C89">
-        <v>4089.893303839037</v>
+        <v>3938.22648586962</v>
       </c>
       <c r="D89">
-        <v>17275.59730383904</v>
+        <v>17301.32248586962</v>
       </c>
       <c r="E89">
-        <v>10103.004</v>
+        <v>10280.396</v>
       </c>
       <c r="F89">
-        <v>15433.104</v>
+        <v>15610.496</v>
       </c>
       <c r="G89">
         <v>2247.4</v>
@@ -8591,28 +8591,28 @@
         <v>2683.5</v>
       </c>
       <c r="M89">
-        <v>853.4506512</v>
+        <v>863.2604288000001</v>
       </c>
       <c r="N89">
-        <v>1830.0493488</v>
+        <v>1820.2395712</v>
       </c>
       <c r="O89">
-        <v>384.310363248</v>
+        <v>382.250309952</v>
       </c>
       <c r="P89">
-        <v>1445.738985552</v>
+        <v>1437.989261248</v>
       </c>
       <c r="Q89">
-        <v>2336.838985552</v>
+        <v>2329.089261248</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3943933291261935</v>
+        <v>0.4224724443031678</v>
       </c>
       <c r="T89">
-        <v>5.877784325776961</v>
+        <v>6.35123854672437</v>
       </c>
       <c r="U89">
         <v>0.0553</v>
@@ -8629,7 +8629,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>3.144294279026968</v>
+        <v>3.108563662219842</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8637,22 +8637,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.08914125331638015</v>
+        <v>0.08900368384635511</v>
       </c>
       <c r="C90">
-        <v>3938.22648586962</v>
+        <v>3786.636397163567</v>
       </c>
       <c r="D90">
-        <v>17301.32248586962</v>
+        <v>17327.12439716357</v>
       </c>
       <c r="E90">
-        <v>10280.396</v>
+        <v>10457.788</v>
       </c>
       <c r="F90">
-        <v>15610.496</v>
+        <v>15787.888</v>
       </c>
       <c r="G90">
         <v>2247.4</v>
@@ -8673,28 +8673,28 @@
         <v>2683.5</v>
       </c>
       <c r="M90">
-        <v>863.2604288000001</v>
+        <v>873.0702064000001</v>
       </c>
       <c r="N90">
-        <v>1820.2395712</v>
+        <v>1810.4297936</v>
       </c>
       <c r="O90">
-        <v>382.250309952</v>
+        <v>380.190256656</v>
       </c>
       <c r="P90">
-        <v>1437.989261248</v>
+        <v>1430.239536944</v>
       </c>
       <c r="Q90">
-        <v>2329.089261248</v>
+        <v>2321.339536944</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.4224724443031678</v>
+        <v>0.4556568531486829</v>
       </c>
       <c r="T90">
-        <v>6.35123854672437</v>
+        <v>6.91077535329858</v>
       </c>
       <c r="U90">
         <v>0.0553</v>
@@ -8711,7 +8711,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>3.108563662219842</v>
+        <v>3.073635980621867</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8719,22 +8719,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.08900368384635511</v>
+        <v>0.0888661143763301</v>
       </c>
       <c r="C91">
-        <v>3786.636397163567</v>
+        <v>3635.123381518615</v>
       </c>
       <c r="D91">
-        <v>17327.12439716357</v>
+        <v>17353.00338151861</v>
       </c>
       <c r="E91">
-        <v>10457.788</v>
+        <v>10635.18</v>
       </c>
       <c r="F91">
-        <v>15787.888</v>
+        <v>15965.28</v>
       </c>
       <c r="G91">
         <v>2247.4</v>
@@ -8755,28 +8755,28 @@
         <v>2683.5</v>
       </c>
       <c r="M91">
-        <v>873.0702064000001</v>
+        <v>882.879984</v>
       </c>
       <c r="N91">
-        <v>1810.4297936</v>
+        <v>1800.620016</v>
       </c>
       <c r="O91">
-        <v>380.190256656</v>
+        <v>378.1302033599999</v>
       </c>
       <c r="P91">
-        <v>1430.239536944</v>
+        <v>1422.48981264</v>
       </c>
       <c r="Q91">
-        <v>2321.339536944</v>
+        <v>2313.58981264</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.4556568531486829</v>
+        <v>0.495478143763301</v>
       </c>
       <c r="T91">
-        <v>6.91077535329858</v>
+        <v>7.582219521187633</v>
       </c>
       <c r="U91">
         <v>0.0553</v>
@@ -8793,7 +8793,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>3.073635980621867</v>
+        <v>3.039484469726069</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8801,22 +8801,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.0888661143763301</v>
+        <v>0.08872854490630505</v>
       </c>
       <c r="C92">
-        <v>3635.123381518615</v>
+        <v>3483.68778478951</v>
       </c>
       <c r="D92">
-        <v>17353.00338151861</v>
+        <v>17378.95978478951</v>
       </c>
       <c r="E92">
-        <v>10635.18</v>
+        <v>10812.572</v>
       </c>
       <c r="F92">
-        <v>15965.28</v>
+        <v>16142.672</v>
       </c>
       <c r="G92">
         <v>2247.4</v>
@@ -8837,28 +8837,28 @@
         <v>2683.5</v>
       </c>
       <c r="M92">
-        <v>882.879984</v>
+        <v>892.6897616000001</v>
       </c>
       <c r="N92">
-        <v>1800.620016</v>
+        <v>1790.8102384</v>
       </c>
       <c r="O92">
-        <v>378.1302033599999</v>
+        <v>376.070150064</v>
       </c>
       <c r="P92">
-        <v>1422.48981264</v>
+        <v>1414.740088336</v>
       </c>
       <c r="Q92">
-        <v>2313.58981264</v>
+        <v>2305.840088336</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.495478143763301</v>
+        <v>0.5441486100700563</v>
       </c>
       <c r="T92">
-        <v>7.582219521187633</v>
+        <v>8.402873504163139</v>
       </c>
       <c r="U92">
         <v>0.0553</v>
@@ -8875,7 +8875,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>3.039484469726069</v>
+        <v>3.00608354148732</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8883,22 +8883,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.08872854490630505</v>
+        <v>0.09040797543628006</v>
       </c>
       <c r="C93">
-        <v>3483.68778478951</v>
+        <v>2994.640301008785</v>
       </c>
       <c r="D93">
-        <v>17378.95978478951</v>
+        <v>17067.30430100879</v>
       </c>
       <c r="E93">
-        <v>10812.572</v>
+        <v>10989.964</v>
       </c>
       <c r="F93">
-        <v>16142.672</v>
+        <v>16320.064</v>
       </c>
       <c r="G93">
         <v>2247.4</v>
@@ -8919,45 +8919,45 @@
         <v>2683.5</v>
       </c>
       <c r="M93">
-        <v>892.6897616000001</v>
+        <v>943.2996992000002</v>
       </c>
       <c r="N93">
-        <v>1790.8102384</v>
+        <v>1740.2003008</v>
       </c>
       <c r="O93">
-        <v>376.070150064</v>
+        <v>365.4420631679999</v>
       </c>
       <c r="P93">
-        <v>1414.740088336</v>
+        <v>1374.758237632</v>
       </c>
       <c r="Q93">
-        <v>2305.840088336</v>
+        <v>2265.858237632</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.5441486100700563</v>
+        <v>0.6049866929535008</v>
       </c>
       <c r="T93">
-        <v>8.402873504163139</v>
+        <v>9.428690982882527</v>
       </c>
       <c r="U93">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V93">
         <v>0.21</v>
       </c>
       <c r="W93">
-        <v>0.043687</v>
+        <v>0.04566200000000001</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y93">
-        <v>3.00608354148732</v>
+        <v>2.844801076768964</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8965,22 +8965,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.09040797543628006</v>
+        <v>0.09029015596625503</v>
       </c>
       <c r="C94">
-        <v>2994.640301008785</v>
+        <v>2838.747271613305</v>
       </c>
       <c r="D94">
-        <v>17067.30430100879</v>
+        <v>17088.80327161331</v>
       </c>
       <c r="E94">
-        <v>10989.964</v>
+        <v>11167.356</v>
       </c>
       <c r="F94">
-        <v>16320.064</v>
+        <v>16497.456</v>
       </c>
       <c r="G94">
         <v>2247.4</v>
@@ -9001,28 +9001,28 @@
         <v>2683.5</v>
       </c>
       <c r="M94">
-        <v>943.2996992000002</v>
+        <v>953.5529568000002</v>
       </c>
       <c r="N94">
-        <v>1740.2003008</v>
+        <v>1729.9470432</v>
       </c>
       <c r="O94">
-        <v>365.4420631679999</v>
+        <v>363.2888790719999</v>
       </c>
       <c r="P94">
-        <v>1374.758237632</v>
+        <v>1366.658164128</v>
       </c>
       <c r="Q94">
-        <v>2265.858237632</v>
+        <v>2257.758164128</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.6049866929535008</v>
+        <v>0.683207085232215</v>
       </c>
       <c r="T94">
-        <v>9.428690982882527</v>
+        <v>10.74759916980745</v>
       </c>
       <c r="U94">
         <v>0.0578</v>
@@ -9039,7 +9039,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>2.844801076768964</v>
+        <v>2.814211817878975</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9047,22 +9047,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.09029015596625503</v>
+        <v>0.09017233649622999</v>
       </c>
       <c r="C95">
-        <v>2838.747271613305</v>
+        <v>2682.908473241601</v>
       </c>
       <c r="D95">
-        <v>17088.80327161331</v>
+        <v>17110.3564732416</v>
       </c>
       <c r="E95">
-        <v>11167.356</v>
+        <v>11344.748</v>
       </c>
       <c r="F95">
-        <v>16497.456</v>
+        <v>16674.848</v>
       </c>
       <c r="G95">
         <v>2247.4</v>
@@ -9083,28 +9083,28 @@
         <v>2683.5</v>
       </c>
       <c r="M95">
-        <v>953.5529568000002</v>
+        <v>963.8062144000002</v>
       </c>
       <c r="N95">
-        <v>1729.9470432</v>
+        <v>1719.6937856</v>
       </c>
       <c r="O95">
-        <v>363.2888790719999</v>
+        <v>361.135694976</v>
       </c>
       <c r="P95">
-        <v>1366.658164128</v>
+        <v>1358.558090624</v>
       </c>
       <c r="Q95">
-        <v>2257.758164128</v>
+        <v>2249.658090624</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.683207085232215</v>
+        <v>0.787500941603834</v>
       </c>
       <c r="T95">
-        <v>10.74759916980745</v>
+        <v>12.50614341904069</v>
       </c>
       <c r="U95">
         <v>0.0578</v>
@@ -9121,7 +9121,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>2.814211817878975</v>
+        <v>2.784273394284518</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9129,22 +9129,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.09017233649622999</v>
+        <v>0.09005451702620498</v>
       </c>
       <c r="C96">
-        <v>2682.908473241601</v>
+        <v>2527.124111348941</v>
       </c>
       <c r="D96">
-        <v>17110.3564732416</v>
+        <v>17131.96411134894</v>
       </c>
       <c r="E96">
-        <v>11344.748</v>
+        <v>11522.14</v>
       </c>
       <c r="F96">
-        <v>16674.848</v>
+        <v>16852.24</v>
       </c>
       <c r="G96">
         <v>2247.4</v>
@@ -9165,28 +9165,28 @@
         <v>2683.5</v>
       </c>
       <c r="M96">
-        <v>963.8062144000002</v>
+        <v>974.0594720000001</v>
       </c>
       <c r="N96">
-        <v>1719.6937856</v>
+        <v>1709.440528</v>
       </c>
       <c r="O96">
-        <v>361.135694976</v>
+        <v>358.9825108799999</v>
       </c>
       <c r="P96">
-        <v>1358.558090624</v>
+        <v>1350.45801712</v>
       </c>
       <c r="Q96">
-        <v>2249.658090624</v>
+        <v>2241.55801712</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.787500941603834</v>
+        <v>0.9335123405241007</v>
       </c>
       <c r="T96">
-        <v>12.50614341904069</v>
+        <v>14.96810536796722</v>
       </c>
       <c r="U96">
         <v>0.0578</v>
@@ -9203,7 +9203,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>2.784273394284518</v>
+        <v>2.754965253292049</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9211,22 +9211,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.09005451702620498</v>
+        <v>0.08993669755617996</v>
       </c>
       <c r="C97">
-        <v>2527.124111348941</v>
+        <v>2371.394392429749</v>
       </c>
       <c r="D97">
-        <v>17131.96411134894</v>
+        <v>17153.62639242975</v>
       </c>
       <c r="E97">
-        <v>11522.14</v>
+        <v>11699.532</v>
       </c>
       <c r="F97">
-        <v>16852.24</v>
+        <v>17029.632</v>
       </c>
       <c r="G97">
         <v>2247.4</v>
@@ -9247,28 +9247,28 @@
         <v>2683.5</v>
       </c>
       <c r="M97">
-        <v>974.0594720000001</v>
+        <v>984.3127296000001</v>
       </c>
       <c r="N97">
-        <v>1709.440528</v>
+        <v>1699.1872704</v>
       </c>
       <c r="O97">
-        <v>358.9825108799999</v>
+        <v>356.8293267839999</v>
       </c>
       <c r="P97">
-        <v>1350.45801712</v>
+        <v>1342.357943616</v>
       </c>
       <c r="Q97">
-        <v>2241.55801712</v>
+        <v>2233.457943616</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.9335123405241007</v>
+        <v>1.152529438904501</v>
       </c>
       <c r="T97">
-        <v>14.96810536796722</v>
+        <v>18.66104829135701</v>
       </c>
       <c r="U97">
         <v>0.0578</v>
@@ -9285,7 +9285,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>2.754965253292049</v>
+        <v>2.726267698570257</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9293,22 +9293,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.08993669755617997</v>
+        <v>0.08981887808615495</v>
       </c>
       <c r="C98">
-        <v>2371.394392429745</v>
+        <v>2215.719524024156</v>
       </c>
       <c r="D98">
-        <v>17153.62639242975</v>
+        <v>17175.34352402416</v>
       </c>
       <c r="E98">
-        <v>11699.532</v>
+        <v>11876.924</v>
       </c>
       <c r="F98">
-        <v>17029.632</v>
+        <v>17207.024</v>
       </c>
       <c r="G98">
         <v>2247.4</v>
@@ -9329,28 +9329,28 @@
         <v>2683.5</v>
       </c>
       <c r="M98">
-        <v>984.3127296000001</v>
+        <v>994.5659872000001</v>
       </c>
       <c r="N98">
-        <v>1699.1872704</v>
+        <v>1688.9340128</v>
       </c>
       <c r="O98">
-        <v>356.8293267839999</v>
+        <v>354.676142688</v>
       </c>
       <c r="P98">
-        <v>1342.357943616</v>
+        <v>1334.257870112</v>
       </c>
       <c r="Q98">
-        <v>2233.457943616</v>
+        <v>2225.357870112</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.152529438904498</v>
+        <v>1.517557936205163</v>
       </c>
       <c r="T98">
-        <v>18.66104829135696</v>
+        <v>24.81595316367327</v>
       </c>
       <c r="U98">
         <v>0.0578</v>
@@ -9367,7 +9367,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>2.726267698570257</v>
+        <v>2.698161846007677</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9375,22 +9375,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.08981887808615495</v>
+        <v>0.08970105861612991</v>
       </c>
       <c r="C99">
-        <v>2215.719524024156</v>
+        <v>2060.099714724649</v>
       </c>
       <c r="D99">
-        <v>17175.34352402416</v>
+        <v>17197.11571472465</v>
       </c>
       <c r="E99">
-        <v>11876.924</v>
+        <v>12054.316</v>
       </c>
       <c r="F99">
-        <v>17207.024</v>
+        <v>17384.416</v>
       </c>
       <c r="G99">
         <v>2247.4</v>
@@ -9411,28 +9411,28 @@
         <v>2683.5</v>
       </c>
       <c r="M99">
-        <v>994.5659872000001</v>
+        <v>1004.8192448</v>
       </c>
       <c r="N99">
-        <v>1688.9340128</v>
+        <v>1678.6807552</v>
       </c>
       <c r="O99">
-        <v>354.676142688</v>
+        <v>352.522958592</v>
       </c>
       <c r="P99">
-        <v>1334.257870112</v>
+        <v>1326.157796608</v>
       </c>
       <c r="Q99">
-        <v>2225.357870112</v>
+        <v>2217.257796608</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.517557936205163</v>
+        <v>2.247614930806493</v>
       </c>
       <c r="T99">
-        <v>24.81595316367327</v>
+        <v>37.12576290830586</v>
       </c>
       <c r="U99">
         <v>0.0578</v>
@@ -9449,7 +9449,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>2.698161846007677</v>
+        <v>2.670629582272905</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9457,22 +9457,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.08970105861612991</v>
+        <v>0.0895832391461049</v>
       </c>
       <c r="C100">
-        <v>2060.099714724649</v>
+        <v>1904.535174182725</v>
       </c>
       <c r="D100">
-        <v>17197.11571472465</v>
+        <v>17218.94317418272</v>
       </c>
       <c r="E100">
-        <v>12054.316</v>
+        <v>12231.708</v>
       </c>
       <c r="F100">
-        <v>17384.416</v>
+        <v>17561.808</v>
       </c>
       <c r="G100">
         <v>2247.4</v>
@@ -9493,28 +9493,28 @@
         <v>2683.5</v>
       </c>
       <c r="M100">
-        <v>1004.8192448</v>
+        <v>1015.0725024</v>
       </c>
       <c r="N100">
-        <v>1678.6807552</v>
+        <v>1668.4274976</v>
       </c>
       <c r="O100">
-        <v>352.522958592</v>
+        <v>350.369774496</v>
       </c>
       <c r="P100">
-        <v>1326.157796608</v>
+        <v>1318.057723104</v>
       </c>
       <c r="Q100">
-        <v>2217.257796608</v>
+        <v>2209.157723104</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.247614930806493</v>
+        <v>4.437785914610485</v>
       </c>
       <c r="T100">
-        <v>37.12576290830586</v>
+        <v>74.05519214220367</v>
       </c>
       <c r="U100">
         <v>0.0578</v>
@@ -9531,91 +9531,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>2.670629582272905</v>
+        <v>2.64365352588631</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.0895832391461049</v>
-      </c>
-      <c r="C101">
-        <v>1904.535174182725</v>
-      </c>
-      <c r="D101">
-        <v>17218.94317418272</v>
-      </c>
-      <c r="E101">
-        <v>12231.708</v>
-      </c>
-      <c r="F101">
-        <v>17561.808</v>
-      </c>
-      <c r="G101">
-        <v>2247.4</v>
-      </c>
-      <c r="H101">
-        <v>12409.1</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>3574.6</v>
-      </c>
-      <c r="K101">
-        <v>891.1</v>
-      </c>
-      <c r="L101">
-        <v>2683.5</v>
-      </c>
-      <c r="M101">
-        <v>1015.0725024</v>
-      </c>
-      <c r="N101">
-        <v>1668.4274976</v>
-      </c>
-      <c r="O101">
-        <v>350.369774496</v>
-      </c>
-      <c r="P101">
-        <v>1318.057723104</v>
-      </c>
-      <c r="Q101">
-        <v>2209.157723104</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>4.437785914610485</v>
-      </c>
-      <c r="T101">
-        <v>74.05519214220367</v>
-      </c>
-      <c r="U101">
-        <v>0.0578</v>
-      </c>
-      <c r="V101">
-        <v>0.21</v>
-      </c>
-      <c r="W101">
-        <v>0.04566200000000001</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>Baa2/BBB</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>2.64365352588631</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
